--- a/08_sampledata.xlsx
+++ b/08_sampledata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/65f33c3464bcf092/Research/2018-2022_Sado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="8_{C96D46A6-B296-FB4D-A5F1-3DE4A23156A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8914479-5D84-AE4A-8866-6DE9176A99B8}"/>
+  <xr:revisionPtr revIDLastSave="335" documentId="8_{C96D46A6-B296-FB4D-A5F1-3DE4A23156A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71A64F87-3ED3-514B-8C07-460D991ADC10}"/>
   <bookViews>
-    <workbookView xWindow="13260" yWindow="500" windowWidth="55540" windowHeight="28300" xr2:uid="{3521B622-29B9-CA4D-8B15-F4EE5C51B8FD}"/>
+    <workbookView xWindow="7940" yWindow="600" windowWidth="27160" windowHeight="27760" xr2:uid="{3521B622-29B9-CA4D-8B15-F4EE5C51B8FD}"/>
   </bookViews>
   <sheets>
     <sheet name="08_sampledat" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3106" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="930">
   <si>
     <t>2018-001-S</t>
   </si>
@@ -2903,6 +2903,14 @@
   </si>
   <si>
     <t>sample</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ph</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>ec</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -2910,6 +2918,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="182" formatCode="0.0_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="12"/>
@@ -3496,7 +3509,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3504,6 +3517,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3881,7 +3903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9ADA172-3B91-DD47-983F-84F53C83B4DF}">
-  <dimension ref="A1:S298"/>
+  <dimension ref="A1:U298"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="21" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="20.140625" style="1" bestFit="1" customWidth="1"/>
@@ -3902,10 +3924,12 @@
     <col min="16" max="16" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="4" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>927</v>
       </c>
@@ -3960,11 +3984,17 @@
       <c r="R1" t="s">
         <v>925</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="5" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="U1" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4019,11 +4049,17 @@
       <c r="R2">
         <v>25.8</v>
       </c>
-      <c r="S2">
+      <c r="S2" s="5">
         <v>1936.15</v>
       </c>
-    </row>
-    <row r="3" spans="1:19">
+      <c r="T2" s="4">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="U2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -4078,11 +4114,17 @@
       <c r="R3">
         <v>17.5</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="5">
         <v>336.24</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="T3" s="4">
+        <v>7.17</v>
+      </c>
+      <c r="U3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -4137,11 +4179,17 @@
       <c r="R4">
         <v>23</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="5">
         <v>813.79</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" s="4">
+        <v>7.67</v>
+      </c>
+      <c r="U4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -4196,11 +4244,17 @@
       <c r="R5">
         <v>27.2</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="5">
         <v>1097.42</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U5">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -4255,11 +4309,17 @@
       <c r="R6">
         <v>22.4</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="5">
         <v>1596.32</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6" s="4">
+        <v>7.96</v>
+      </c>
+      <c r="U6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -4314,11 +4374,17 @@
       <c r="R7">
         <v>25.7</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="5">
         <v>35.020000000000003</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7" s="4">
+        <v>7.52</v>
+      </c>
+      <c r="U7">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -4373,11 +4439,17 @@
       <c r="R8">
         <v>26.2</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="5">
         <v>933.72</v>
       </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8" s="4">
+        <v>7.32</v>
+      </c>
+      <c r="U8">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -4432,11 +4504,17 @@
       <c r="R9">
         <v>24.2</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="5">
         <v>329.71</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9" s="4">
+        <v>8.08</v>
+      </c>
+      <c r="U9">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -4491,11 +4569,17 @@
       <c r="R10">
         <v>27.6</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="5">
         <v>1683.25</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10" s="4">
+        <v>7.51</v>
+      </c>
+      <c r="U10">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -4550,11 +4634,17 @@
       <c r="R11">
         <v>24.8</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="5">
         <v>16.07</v>
       </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11" s="4">
+        <v>8.66</v>
+      </c>
+      <c r="U11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -4609,11 +4699,17 @@
       <c r="R12">
         <v>25.2</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="5">
         <v>309.79000000000002</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U12">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -4668,11 +4764,17 @@
       <c r="R13">
         <v>22.9</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="5">
         <v>71.63</v>
       </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="T13" s="4">
+        <v>8.25</v>
+      </c>
+      <c r="U13">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -4727,11 +4829,17 @@
       <c r="R14">
         <v>26.2</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="5">
         <v>417.23</v>
       </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14" s="4">
+        <v>7.74</v>
+      </c>
+      <c r="U14">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -4786,11 +4894,17 @@
       <c r="R15">
         <v>25.1</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="5">
         <v>240.29</v>
       </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U15">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -4845,11 +4959,17 @@
       <c r="R16">
         <v>25.2</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="5">
         <v>524.02</v>
       </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="T16" s="4">
+        <v>7.65</v>
+      </c>
+      <c r="U16">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -4859,8 +4979,9 @@
       <c r="C17">
         <v>2018</v>
       </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="U17" s="3"/>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -4915,11 +5036,17 @@
       <c r="R18">
         <v>25.8</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="5">
         <v>1936.15</v>
       </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="T18" s="4">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="U18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -4974,11 +5101,17 @@
       <c r="R19">
         <v>25.8</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="5">
         <v>1936.15</v>
       </c>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19" s="4">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="U19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -5033,11 +5166,17 @@
       <c r="R20">
         <v>25.3</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="5">
         <v>148.74</v>
       </c>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="T20" s="4">
+        <v>8.59</v>
+      </c>
+      <c r="U20">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -5092,11 +5231,17 @@
       <c r="R21">
         <v>20.8</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="5">
         <v>22.08</v>
       </c>
-    </row>
-    <row r="22" spans="1:19">
+      <c r="T21" s="4">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="U21">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -5151,11 +5296,17 @@
       <c r="R22">
         <v>23.2</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="5">
         <v>428.55</v>
       </c>
-    </row>
-    <row r="23" spans="1:19">
+      <c r="T22" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="U22">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -5210,11 +5361,17 @@
       <c r="R23">
         <v>27.3</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="5">
         <v>98.12</v>
       </c>
-    </row>
-    <row r="24" spans="1:19">
+      <c r="T23" s="4">
+        <v>8.59</v>
+      </c>
+      <c r="U23">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -5269,11 +5426,17 @@
       <c r="R24">
         <v>22</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="5">
         <v>8.57</v>
       </c>
-    </row>
-    <row r="25" spans="1:19">
+      <c r="T24" s="4">
+        <v>7.52</v>
+      </c>
+      <c r="U24">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -5328,11 +5491,17 @@
       <c r="R25">
         <v>25.1</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="5">
         <v>948.37</v>
       </c>
-    </row>
-    <row r="26" spans="1:19">
+      <c r="T25" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -5387,11 +5556,17 @@
       <c r="R26">
         <v>24.7</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="5">
         <v>206.32</v>
       </c>
-    </row>
-    <row r="27" spans="1:19">
+      <c r="T26" s="4">
+        <v>7.35</v>
+      </c>
+      <c r="U26">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -5446,11 +5621,17 @@
       <c r="R27">
         <v>24.8</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="5">
         <v>87.9</v>
       </c>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="T27" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="U27">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -5505,11 +5686,17 @@
       <c r="R28">
         <v>21.2</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="5">
         <v>24.01</v>
       </c>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="T28" s="4">
+        <v>7.49</v>
+      </c>
+      <c r="U28">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -5564,11 +5751,17 @@
       <c r="R29">
         <v>21.3</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="5">
         <v>558.86</v>
       </c>
-    </row>
-    <row r="30" spans="1:19">
+      <c r="T29" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="U29">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -5623,11 +5816,17 @@
       <c r="R30">
         <v>21.3</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="5">
         <v>558.86</v>
       </c>
-    </row>
-    <row r="31" spans="1:19">
+      <c r="T30" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="U30">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -5682,11 +5881,17 @@
       <c r="R31">
         <v>22.2</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="5">
         <v>823.3</v>
       </c>
-    </row>
-    <row r="32" spans="1:19">
+      <c r="T31" s="4">
+        <v>7.95</v>
+      </c>
+      <c r="U31">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -5741,11 +5946,17 @@
       <c r="R32">
         <v>19.5</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="5">
         <v>925</v>
       </c>
-    </row>
-    <row r="33" spans="1:19">
+      <c r="T32" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="U32">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -5800,11 +6011,17 @@
       <c r="R33">
         <v>19.399999999999999</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="5">
         <v>89.31</v>
       </c>
-    </row>
-    <row r="34" spans="1:19">
+      <c r="T33" s="4">
+        <v>7.68</v>
+      </c>
+      <c r="U33">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -5859,11 +6076,17 @@
       <c r="R34">
         <v>20.8</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="5">
         <v>653.33000000000004</v>
       </c>
-    </row>
-    <row r="35" spans="1:19">
+      <c r="T34" s="4">
+        <v>7.97</v>
+      </c>
+      <c r="U34">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -5918,11 +6141,17 @@
       <c r="R35">
         <v>21.1</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="5">
         <v>244.97</v>
       </c>
-    </row>
-    <row r="36" spans="1:19">
+      <c r="T35" s="4">
+        <v>7.38</v>
+      </c>
+      <c r="U35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -5977,11 +6206,17 @@
       <c r="R36">
         <v>22.3</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="5">
         <v>106.86</v>
       </c>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="T36" s="4">
+        <v>8.07</v>
+      </c>
+      <c r="U36">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -6036,11 +6271,17 @@
       <c r="R37">
         <v>21.4</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="5">
         <v>20.25</v>
       </c>
-    </row>
-    <row r="38" spans="1:19">
+      <c r="T37" s="4">
+        <v>7.41</v>
+      </c>
+      <c r="U37">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -6095,11 +6336,17 @@
       <c r="R38">
         <v>21.8</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="5">
         <v>39.33</v>
       </c>
-    </row>
-    <row r="39" spans="1:19">
+      <c r="T38" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="U38">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -6154,11 +6401,17 @@
       <c r="R39">
         <v>20.399999999999999</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="5">
         <v>79.930000000000007</v>
       </c>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="T39" s="4">
+        <v>7.46</v>
+      </c>
+      <c r="U39">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -6213,11 +6466,17 @@
       <c r="R40">
         <v>20.399999999999999</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="5">
         <v>79.930000000000007</v>
       </c>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="T40" s="4">
+        <v>7.46</v>
+      </c>
+      <c r="U40">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -6272,11 +6531,17 @@
       <c r="R41">
         <v>21.6</v>
       </c>
-      <c r="S41">
+      <c r="S41" s="5">
         <v>71.89</v>
       </c>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="T41" s="4">
+        <v>7.75</v>
+      </c>
+      <c r="U41">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -6331,11 +6596,17 @@
       <c r="R42">
         <v>20.7</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="5">
         <v>81.3</v>
       </c>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="T42" s="4">
+        <v>8.1</v>
+      </c>
+      <c r="U42">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
@@ -6390,11 +6661,17 @@
       <c r="R43">
         <v>22.1</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="5">
         <v>138.44999999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:19">
+      <c r="T43" s="4">
+        <v>7.69</v>
+      </c>
+      <c r="U43">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
@@ -6449,11 +6726,17 @@
       <c r="R44">
         <v>19.399999999999999</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="5">
         <v>85.84</v>
       </c>
-    </row>
-    <row r="45" spans="1:19">
+      <c r="T44" s="4">
+        <v>7.62</v>
+      </c>
+      <c r="U44">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -6508,11 +6791,17 @@
       <c r="R45">
         <v>22.6</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="5">
         <v>445.17</v>
       </c>
-    </row>
-    <row r="46" spans="1:19">
+      <c r="T45" s="4">
+        <v>8.06</v>
+      </c>
+      <c r="U45">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
@@ -6567,11 +6856,17 @@
       <c r="R46">
         <v>21.3</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="5">
         <v>6.82</v>
       </c>
-    </row>
-    <row r="47" spans="1:19">
+      <c r="T46" s="4">
+        <v>7.74</v>
+      </c>
+      <c r="U46">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -6626,11 +6921,17 @@
       <c r="R47">
         <v>19.7</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="5">
         <v>210.15</v>
       </c>
-    </row>
-    <row r="48" spans="1:19">
+      <c r="T47" s="4">
+        <v>7.36</v>
+      </c>
+      <c r="U47">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -6685,11 +6986,17 @@
       <c r="R48">
         <v>24.4</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="5">
         <v>176.68</v>
       </c>
-    </row>
-    <row r="49" spans="1:19">
+      <c r="T48" s="4">
+        <v>7.51</v>
+      </c>
+      <c r="U48">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
@@ -6744,11 +7051,17 @@
       <c r="R49">
         <v>24.5</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="5">
         <v>126.47</v>
       </c>
-    </row>
-    <row r="50" spans="1:19">
+      <c r="T49" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="U49">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -6803,11 +7116,17 @@
       <c r="R50">
         <v>24.5</v>
       </c>
-      <c r="S50">
+      <c r="S50" s="5">
         <v>126.47</v>
       </c>
-    </row>
-    <row r="51" spans="1:19">
+      <c r="T50" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="U50">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -6862,11 +7181,17 @@
       <c r="R51">
         <v>21.6</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="5">
         <v>541.14</v>
       </c>
-    </row>
-    <row r="52" spans="1:19">
+      <c r="T51" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U51">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -6921,11 +7246,17 @@
       <c r="R52">
         <v>23.3</v>
       </c>
-      <c r="S52">
+      <c r="S52" s="5">
         <v>1103.4000000000001</v>
       </c>
-    </row>
-    <row r="53" spans="1:19">
+      <c r="T52" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U52">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -6980,11 +7311,17 @@
       <c r="R53">
         <v>24.5</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="5">
         <v>766.02</v>
       </c>
-    </row>
-    <row r="54" spans="1:19">
+      <c r="T53" s="4">
+        <v>8</v>
+      </c>
+      <c r="U53">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
@@ -7039,11 +7376,17 @@
       <c r="R54">
         <v>23.3</v>
       </c>
-      <c r="S54">
+      <c r="S54" s="5">
         <v>9.06</v>
       </c>
-    </row>
-    <row r="55" spans="1:19">
+      <c r="T54" s="4">
+        <v>7.35</v>
+      </c>
+      <c r="U54">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
@@ -7098,11 +7441,17 @@
       <c r="R55">
         <v>25.5</v>
       </c>
-      <c r="S55">
+      <c r="S55" s="5">
         <v>940.72</v>
       </c>
-    </row>
-    <row r="56" spans="1:19">
+      <c r="T55" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U55">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21">
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
@@ -7157,11 +7506,17 @@
       <c r="R56">
         <v>30.4</v>
       </c>
-      <c r="S56">
+      <c r="S56" s="5">
         <v>15.48</v>
       </c>
-    </row>
-    <row r="57" spans="1:19">
+      <c r="T56" s="4">
+        <v>7.93</v>
+      </c>
+      <c r="U56">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21">
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
@@ -7216,11 +7571,17 @@
       <c r="R57">
         <v>24.5</v>
       </c>
-      <c r="S57">
+      <c r="S57" s="5">
         <v>123.82</v>
       </c>
-    </row>
-    <row r="58" spans="1:19">
+      <c r="T57" s="4">
+        <v>7.93</v>
+      </c>
+      <c r="U57">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21">
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
@@ -7275,11 +7636,17 @@
       <c r="R58">
         <v>31.8</v>
       </c>
-      <c r="S58">
+      <c r="S58" s="5">
         <v>1234.1600000000001</v>
       </c>
-    </row>
-    <row r="59" spans="1:19">
+      <c r="T58" s="4">
+        <v>8.42</v>
+      </c>
+      <c r="U58">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -7334,11 +7701,17 @@
       <c r="R59">
         <v>25.3</v>
       </c>
-      <c r="S59">
+      <c r="S59" s="5">
         <v>2158.34</v>
       </c>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="T59" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U59">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -7393,11 +7766,17 @@
       <c r="R60">
         <v>24.5</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="5">
         <v>96.27</v>
       </c>
-    </row>
-    <row r="61" spans="1:19">
+      <c r="T60" s="4">
+        <v>7.86</v>
+      </c>
+      <c r="U60">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
@@ -7452,11 +7831,17 @@
       <c r="R61">
         <v>24.5</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="5">
         <v>96.27</v>
       </c>
-    </row>
-    <row r="62" spans="1:19">
+      <c r="T61" s="4">
+        <v>7.86</v>
+      </c>
+      <c r="U61">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -7511,11 +7896,17 @@
       <c r="R62">
         <v>27.8</v>
       </c>
-      <c r="S62">
+      <c r="S62" s="5">
         <v>0.47</v>
       </c>
-    </row>
-    <row r="63" spans="1:19">
+      <c r="T62" s="4">
+        <v>7.67</v>
+      </c>
+      <c r="U62">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
@@ -7570,11 +7961,17 @@
       <c r="R63">
         <v>25.9</v>
       </c>
-      <c r="S63">
+      <c r="S63" s="5">
         <v>66.95</v>
       </c>
-    </row>
-    <row r="64" spans="1:19">
+      <c r="T63" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="U63">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21">
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
@@ -7629,11 +8026,17 @@
       <c r="R64">
         <v>27.4</v>
       </c>
-      <c r="S64">
+      <c r="S64" s="5">
         <v>99.99</v>
       </c>
-    </row>
-    <row r="65" spans="1:19">
+      <c r="T64" s="4">
+        <v>7.65</v>
+      </c>
+      <c r="U64">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -7688,11 +8091,17 @@
       <c r="R65">
         <v>25.3</v>
       </c>
-      <c r="S65">
+      <c r="S65" s="5">
         <v>605.22</v>
       </c>
-    </row>
-    <row r="66" spans="1:19">
+      <c r="T65" s="4">
+        <v>8.17</v>
+      </c>
+      <c r="U65">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
@@ -7747,11 +8156,17 @@
       <c r="R66">
         <v>25.4</v>
       </c>
-      <c r="S66">
+      <c r="S66" s="5">
         <v>60.76</v>
       </c>
-    </row>
-    <row r="67" spans="1:19">
+      <c r="T66" s="4">
+        <v>8.26</v>
+      </c>
+      <c r="U66">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
@@ -7806,11 +8221,17 @@
       <c r="R67">
         <v>21.4</v>
       </c>
-      <c r="S67">
+      <c r="S67" s="5">
         <v>93.16</v>
       </c>
-    </row>
-    <row r="68" spans="1:19">
+      <c r="T67" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U67">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
@@ -7865,11 +8286,17 @@
       <c r="R68">
         <v>25.9</v>
       </c>
-      <c r="S68">
+      <c r="S68" s="5">
         <v>220.55</v>
       </c>
-    </row>
-    <row r="69" spans="1:19">
+      <c r="T68" s="4">
+        <v>7.95</v>
+      </c>
+      <c r="U68">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
@@ -7924,11 +8351,17 @@
       <c r="R69">
         <v>23.8</v>
       </c>
-      <c r="S69">
+      <c r="S69" s="5">
         <v>35.01</v>
       </c>
-    </row>
-    <row r="70" spans="1:19">
+      <c r="T69" s="4">
+        <v>7.92</v>
+      </c>
+      <c r="U69">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
@@ -7983,11 +8416,17 @@
       <c r="R70">
         <v>23.8</v>
       </c>
-      <c r="S70">
+      <c r="S70" s="5">
         <v>35.01</v>
       </c>
-    </row>
-    <row r="71" spans="1:19">
+      <c r="T70" s="4">
+        <v>7.92</v>
+      </c>
+      <c r="U70">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
@@ -8042,11 +8481,17 @@
       <c r="R71">
         <v>22.5</v>
       </c>
-      <c r="S71">
+      <c r="S71" s="5">
         <v>311.97000000000003</v>
       </c>
-    </row>
-    <row r="72" spans="1:19">
+      <c r="T71" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U71">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21">
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
@@ -8101,11 +8546,17 @@
       <c r="R72">
         <v>23.6</v>
       </c>
-      <c r="S72">
+      <c r="S72" s="5">
         <v>87.84</v>
       </c>
-    </row>
-    <row r="73" spans="1:19">
+      <c r="T72" s="4">
+        <v>8.35</v>
+      </c>
+      <c r="U72">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
@@ -8160,11 +8611,17 @@
       <c r="R73">
         <v>23.4</v>
       </c>
-      <c r="S73">
+      <c r="S73" s="5">
         <v>17.260000000000002</v>
       </c>
-    </row>
-    <row r="74" spans="1:19">
+      <c r="T73" s="4">
+        <v>7.64</v>
+      </c>
+      <c r="U73">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
@@ -8219,11 +8676,17 @@
       <c r="R74">
         <v>22.8</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="5">
         <v>243.5</v>
       </c>
-    </row>
-    <row r="75" spans="1:19">
+      <c r="T74" s="4">
+        <v>8.41</v>
+      </c>
+      <c r="U74">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
@@ -8278,11 +8741,17 @@
       <c r="R75">
         <v>24.6</v>
       </c>
-      <c r="S75">
+      <c r="S75" s="5">
         <v>12.73</v>
       </c>
-    </row>
-    <row r="76" spans="1:19">
+      <c r="T75" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="U75">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
@@ -8337,11 +8806,17 @@
       <c r="R76">
         <v>24.7</v>
       </c>
-      <c r="S76">
+      <c r="S76" s="5">
         <v>43.74</v>
       </c>
-    </row>
-    <row r="77" spans="1:19">
+      <c r="T76" s="4">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="U76">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -8396,11 +8871,17 @@
       <c r="R77">
         <v>26</v>
       </c>
-      <c r="S77">
+      <c r="S77" s="5">
         <v>40.840000000000003</v>
       </c>
-    </row>
-    <row r="78" spans="1:19">
+      <c r="T77" s="4">
+        <v>10.02</v>
+      </c>
+      <c r="U77">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
@@ -8455,11 +8936,17 @@
       <c r="R78">
         <v>19.7</v>
       </c>
-      <c r="S78">
+      <c r="S78" s="5">
         <v>165.95</v>
       </c>
-    </row>
-    <row r="79" spans="1:19">
+      <c r="T78" s="4">
+        <v>7.09</v>
+      </c>
+      <c r="U78">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
@@ -8514,11 +9001,17 @@
       <c r="R79">
         <v>25.6</v>
       </c>
-      <c r="S79">
+      <c r="S79" s="5">
         <v>25.35</v>
       </c>
-    </row>
-    <row r="80" spans="1:19">
+      <c r="T79" s="4">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="U79">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
@@ -8573,11 +9066,17 @@
       <c r="R80">
         <v>25.5</v>
       </c>
-      <c r="S80">
+      <c r="S80" s="5">
         <v>32.11</v>
       </c>
-    </row>
-    <row r="81" spans="1:19">
+      <c r="T80" s="4">
+        <v>9.31</v>
+      </c>
+      <c r="U80">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
@@ -8632,11 +9131,17 @@
       <c r="R81">
         <v>25.5</v>
       </c>
-      <c r="S81">
+      <c r="S81" s="5">
         <v>32.11</v>
       </c>
-    </row>
-    <row r="82" spans="1:19">
+      <c r="T81" s="4">
+        <v>9.31</v>
+      </c>
+      <c r="U81">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
@@ -8691,11 +9196,17 @@
       <c r="R82">
         <v>25</v>
       </c>
-      <c r="S82">
+      <c r="S82" s="5">
         <v>48.09</v>
       </c>
-    </row>
-    <row r="83" spans="1:19">
+      <c r="T82" s="4">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="U82">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
@@ -8750,11 +9261,17 @@
       <c r="R83">
         <v>26.8</v>
       </c>
-      <c r="S83">
+      <c r="S83" s="5">
         <v>327.61</v>
       </c>
-    </row>
-    <row r="84" spans="1:19">
+      <c r="T83" s="4">
+        <v>8.26</v>
+      </c>
+      <c r="U83">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
@@ -8809,11 +9326,17 @@
       <c r="R84">
         <v>24</v>
       </c>
-      <c r="S84">
+      <c r="S84" s="5">
         <v>69.510000000000005</v>
       </c>
-    </row>
-    <row r="85" spans="1:19">
+      <c r="T84" s="4">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="U84">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
@@ -8868,11 +9391,17 @@
       <c r="R85">
         <v>24</v>
       </c>
-      <c r="S85">
+      <c r="S85" s="5">
         <v>39.450000000000003</v>
       </c>
-    </row>
-    <row r="86" spans="1:19">
+      <c r="T85" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="U85">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
@@ -8927,11 +9456,17 @@
       <c r="R86">
         <v>23.4</v>
       </c>
-      <c r="S86">
+      <c r="S86" s="5">
         <v>13.54</v>
       </c>
-    </row>
-    <row r="87" spans="1:19">
+      <c r="T86" s="4">
+        <v>8</v>
+      </c>
+      <c r="U86">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
@@ -8986,11 +9521,17 @@
       <c r="R87">
         <v>23.5</v>
       </c>
-      <c r="S87">
+      <c r="S87" s="5">
         <v>8.5399999999999991</v>
       </c>
-    </row>
-    <row r="88" spans="1:19">
+      <c r="T87" s="4">
+        <v>8.52</v>
+      </c>
+      <c r="U87">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
@@ -9045,11 +9586,17 @@
       <c r="R88">
         <v>25.3</v>
       </c>
-      <c r="S88">
+      <c r="S88" s="5">
         <v>104.39</v>
       </c>
-    </row>
-    <row r="89" spans="1:19">
+      <c r="T88" s="4">
+        <v>7.98</v>
+      </c>
+      <c r="U88">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
@@ -9104,11 +9651,17 @@
       <c r="R89">
         <v>25.1</v>
       </c>
-      <c r="S89">
+      <c r="S89" s="5">
         <v>11.2</v>
       </c>
-    </row>
-    <row r="90" spans="1:19">
+      <c r="T89" s="4">
+        <v>7.64</v>
+      </c>
+      <c r="U89">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
@@ -9163,11 +9716,17 @@
       <c r="R90">
         <v>26.5</v>
       </c>
-      <c r="S90">
+      <c r="S90" s="5">
         <v>52.45</v>
       </c>
-    </row>
-    <row r="91" spans="1:19">
+      <c r="T90" s="4">
+        <v>8.76</v>
+      </c>
+      <c r="U90">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21">
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
@@ -9222,11 +9781,17 @@
       <c r="R91">
         <v>27.2</v>
       </c>
-      <c r="S91">
+      <c r="S91" s="5">
         <v>92.49</v>
       </c>
-    </row>
-    <row r="92" spans="1:19">
+      <c r="T91" s="4">
+        <v>7.98</v>
+      </c>
+      <c r="U91">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21">
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
@@ -9281,11 +9846,17 @@
       <c r="R92">
         <v>26.2</v>
       </c>
-      <c r="S92">
+      <c r="S92" s="5">
         <v>274.68</v>
       </c>
-    </row>
-    <row r="93" spans="1:19">
+      <c r="T92" s="4">
+        <v>7.79</v>
+      </c>
+      <c r="U92">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21">
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
@@ -9340,11 +9911,17 @@
       <c r="R93">
         <v>23</v>
       </c>
-      <c r="S93">
+      <c r="S93" s="5">
         <v>12.3</v>
       </c>
-    </row>
-    <row r="94" spans="1:19">
+      <c r="T93" s="4">
+        <v>8.25</v>
+      </c>
+      <c r="U93">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -9399,11 +9976,17 @@
       <c r="R94">
         <v>22</v>
       </c>
-      <c r="S94">
+      <c r="S94" s="5">
         <v>103.45</v>
       </c>
-    </row>
-    <row r="95" spans="1:19">
+      <c r="T94" s="4">
+        <v>8.43</v>
+      </c>
+      <c r="U94">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -9458,11 +10041,17 @@
       <c r="R95">
         <v>23.4</v>
       </c>
-      <c r="S95">
+      <c r="S95" s="5">
         <v>68.84</v>
       </c>
-    </row>
-    <row r="96" spans="1:19">
+      <c r="T95" s="4">
+        <v>7.97</v>
+      </c>
+      <c r="U95">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
@@ -9517,11 +10106,17 @@
       <c r="R96">
         <v>23.3</v>
       </c>
-      <c r="S96">
+      <c r="S96" s="5">
         <v>134.52000000000001</v>
       </c>
-    </row>
-    <row r="97" spans="1:19">
+      <c r="T96" s="4">
+        <v>7.98</v>
+      </c>
+      <c r="U96">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21">
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
@@ -9576,11 +10171,17 @@
       <c r="R97">
         <v>26.7</v>
       </c>
-      <c r="S97">
+      <c r="S97" s="5">
         <v>54.95</v>
       </c>
-    </row>
-    <row r="98" spans="1:19">
+      <c r="T97" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="U97">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21">
       <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
@@ -9635,11 +10236,17 @@
       <c r="R98">
         <v>27.6</v>
       </c>
-      <c r="S98">
+      <c r="S98" s="5">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="99" spans="1:19">
+      <c r="T98" s="4">
+        <v>7.57</v>
+      </c>
+      <c r="U98">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21">
       <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
@@ -9694,11 +10301,17 @@
       <c r="R99">
         <v>27.6</v>
       </c>
-      <c r="S99">
+      <c r="S99" s="5">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="100" spans="1:19">
+      <c r="T99" s="4">
+        <v>7.57</v>
+      </c>
+      <c r="U99">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21">
       <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
@@ -9753,11 +10366,17 @@
       <c r="R100">
         <v>22.4</v>
       </c>
-      <c r="S100">
+      <c r="S100" s="5">
         <v>19.489999999999998</v>
       </c>
-    </row>
-    <row r="101" spans="1:19">
+      <c r="T100" s="4">
+        <v>7.11</v>
+      </c>
+      <c r="U100">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21">
       <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
@@ -9812,11 +10431,17 @@
       <c r="R101">
         <v>23.1</v>
       </c>
-      <c r="S101">
+      <c r="S101" s="5">
         <v>38.1</v>
       </c>
-    </row>
-    <row r="102" spans="1:19">
+      <c r="T101" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="U101">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21">
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
@@ -9827,7 +10452,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:21">
       <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
@@ -9838,7 +10463,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:21">
       <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
@@ -9849,7 +10474,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:21">
       <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
@@ -9860,7 +10485,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:21">
       <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
@@ -9871,7 +10496,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:21">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
@@ -9926,11 +10551,17 @@
       <c r="R107">
         <v>28.4</v>
       </c>
-      <c r="S107">
+      <c r="S107" s="5">
         <v>67.78</v>
       </c>
-    </row>
-    <row r="108" spans="1:19">
+      <c r="T107" s="4">
+        <v>7.64</v>
+      </c>
+      <c r="U107">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21">
       <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
@@ -9985,11 +10616,17 @@
       <c r="R108">
         <v>23.6</v>
       </c>
-      <c r="S108">
+      <c r="S108" s="5">
         <v>39.71</v>
       </c>
-    </row>
-    <row r="109" spans="1:19">
+      <c r="T108" s="4">
+        <v>7.86</v>
+      </c>
+      <c r="U108">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21">
       <c r="A109" s="1" t="s">
         <v>107</v>
       </c>
@@ -10044,11 +10681,17 @@
       <c r="R109">
         <v>26.4</v>
       </c>
-      <c r="S109">
+      <c r="S109" s="5">
         <v>36.15</v>
       </c>
-    </row>
-    <row r="110" spans="1:19">
+      <c r="T109" s="4">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="U109">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21">
       <c r="A110" s="1" t="s">
         <v>108</v>
       </c>
@@ -10103,11 +10746,17 @@
       <c r="R110">
         <v>25.1</v>
       </c>
-      <c r="S110">
+      <c r="S110" s="5">
         <v>36.01</v>
       </c>
-    </row>
-    <row r="111" spans="1:19">
+      <c r="T110" s="4">
+        <v>7.96</v>
+      </c>
+      <c r="U110">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21">
       <c r="A111" s="1" t="s">
         <v>109</v>
       </c>
@@ -10162,11 +10811,17 @@
       <c r="R111">
         <v>23.5</v>
       </c>
-      <c r="S111">
+      <c r="S111" s="5">
         <v>22.4</v>
       </c>
-    </row>
-    <row r="112" spans="1:19">
+      <c r="T111" s="4">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="U111">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21">
       <c r="A112" s="1" t="s">
         <v>110</v>
       </c>
@@ -10221,11 +10876,17 @@
       <c r="R112">
         <v>24.3</v>
       </c>
-      <c r="S112">
+      <c r="S112" s="5">
         <v>22.1</v>
       </c>
-    </row>
-    <row r="113" spans="1:19">
+      <c r="T112" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="U112">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21">
       <c r="A113" s="1" t="s">
         <v>111</v>
       </c>
@@ -10280,11 +10941,17 @@
       <c r="R113">
         <v>22.9</v>
       </c>
-      <c r="S113">
+      <c r="S113" s="5">
         <v>30.57</v>
       </c>
-    </row>
-    <row r="114" spans="1:19">
+      <c r="T113" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="U113">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21">
       <c r="A114" s="1" t="s">
         <v>112</v>
       </c>
@@ -10339,11 +11006,17 @@
       <c r="R114">
         <v>19.899999999999999</v>
       </c>
-      <c r="S114">
+      <c r="S114" s="5">
         <v>47.87</v>
       </c>
-    </row>
-    <row r="115" spans="1:19">
+      <c r="T114" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U114">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21">
       <c r="A115" s="1" t="s">
         <v>113</v>
       </c>
@@ -10398,11 +11071,17 @@
       <c r="R115">
         <v>28.5</v>
       </c>
-      <c r="S115">
+      <c r="S115" s="5">
         <v>36.799999999999997</v>
       </c>
-    </row>
-    <row r="116" spans="1:19">
+      <c r="T115" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U115">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21">
       <c r="A116" s="1" t="s">
         <v>114</v>
       </c>
@@ -10457,11 +11136,17 @@
       <c r="R116">
         <v>27.3</v>
       </c>
-      <c r="S116">
+      <c r="S116" s="5">
         <v>79.67</v>
       </c>
-    </row>
-    <row r="117" spans="1:19">
+      <c r="T116" s="4">
+        <v>7.44</v>
+      </c>
+      <c r="U116">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21">
       <c r="A117" s="1" t="s">
         <v>115</v>
       </c>
@@ -10516,11 +11201,17 @@
       <c r="R117">
         <v>26.7</v>
       </c>
-      <c r="S117">
+      <c r="S117" s="5">
         <v>38.229999999999997</v>
       </c>
-    </row>
-    <row r="118" spans="1:19">
+      <c r="T117" s="4">
+        <v>7.64</v>
+      </c>
+      <c r="U117">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21">
       <c r="A118" s="1" t="s">
         <v>116</v>
       </c>
@@ -10575,11 +11266,17 @@
       <c r="R118">
         <v>23.8</v>
       </c>
-      <c r="S118">
+      <c r="S118" s="5">
         <v>20.85</v>
       </c>
-    </row>
-    <row r="119" spans="1:19">
+      <c r="T118" s="4">
+        <v>7.79</v>
+      </c>
+      <c r="U118">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21">
       <c r="A119" s="1" t="s">
         <v>117</v>
       </c>
@@ -10634,11 +11331,17 @@
       <c r="R119">
         <v>23.6</v>
       </c>
-      <c r="S119">
+      <c r="S119" s="5">
         <v>15.62</v>
       </c>
-    </row>
-    <row r="120" spans="1:19">
+      <c r="T119" s="4">
+        <v>7.91</v>
+      </c>
+      <c r="U119">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21">
       <c r="A120" s="1" t="s">
         <v>118</v>
       </c>
@@ -10693,11 +11396,17 @@
       <c r="R120">
         <v>24.8</v>
       </c>
-      <c r="S120">
+      <c r="S120" s="5">
         <v>11.7</v>
       </c>
-    </row>
-    <row r="121" spans="1:19">
+      <c r="T120" s="4">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="U120">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21">
       <c r="A121" s="1" t="s">
         <v>119</v>
       </c>
@@ -10752,11 +11461,17 @@
       <c r="R121">
         <v>25.4</v>
       </c>
-      <c r="S121">
+      <c r="S121" s="5">
         <v>36.19</v>
       </c>
-    </row>
-    <row r="122" spans="1:19">
+      <c r="T121" s="4">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="U121">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21">
       <c r="A122" s="1" t="s">
         <v>120</v>
       </c>
@@ -10811,11 +11526,17 @@
       <c r="R122">
         <v>24.6</v>
       </c>
-      <c r="S122">
+      <c r="S122" s="5">
         <v>141.26</v>
       </c>
-    </row>
-    <row r="123" spans="1:19">
+      <c r="T122" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U122">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21">
       <c r="A123" s="1" t="s">
         <v>121</v>
       </c>
@@ -10870,11 +11591,17 @@
       <c r="R123">
         <v>26.6</v>
       </c>
-      <c r="S123">
+      <c r="S123" s="5">
         <v>181.78</v>
       </c>
-    </row>
-    <row r="124" spans="1:19">
+      <c r="T123" s="4">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U123">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21">
       <c r="A124" s="1" t="s">
         <v>122</v>
       </c>
@@ -10929,11 +11656,17 @@
       <c r="R124">
         <v>25.9</v>
       </c>
-      <c r="S124">
+      <c r="S124" s="5">
         <v>35.11</v>
       </c>
-    </row>
-    <row r="125" spans="1:19">
+      <c r="T124" s="4">
+        <v>8.14</v>
+      </c>
+      <c r="U124">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21">
       <c r="A125" s="1" t="s">
         <v>123</v>
       </c>
@@ -10988,11 +11721,17 @@
       <c r="R125">
         <v>25.2</v>
       </c>
-      <c r="S125">
+      <c r="S125" s="5">
         <v>132.76</v>
       </c>
-    </row>
-    <row r="126" spans="1:19">
+      <c r="T125" s="4">
+        <v>7.74</v>
+      </c>
+      <c r="U125">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21">
       <c r="A126" s="1" t="s">
         <v>124</v>
       </c>
@@ -11047,11 +11786,17 @@
       <c r="R126">
         <v>22.8</v>
       </c>
-      <c r="S126">
+      <c r="S126" s="5">
         <v>123.86</v>
       </c>
-    </row>
-    <row r="127" spans="1:19">
+      <c r="T126" s="4">
+        <v>8.24</v>
+      </c>
+      <c r="U126">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21">
       <c r="A127" s="1" t="s">
         <v>125</v>
       </c>
@@ -11106,11 +11851,17 @@
       <c r="R127">
         <v>21.1</v>
       </c>
-      <c r="S127">
+      <c r="S127" s="5">
         <v>128.37</v>
       </c>
-    </row>
-    <row r="128" spans="1:19">
+      <c r="T127" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U127">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21">
       <c r="A128" s="1" t="s">
         <v>126</v>
       </c>
@@ -11165,11 +11916,17 @@
       <c r="R128">
         <v>22.7</v>
       </c>
-      <c r="S128">
+      <c r="S128" s="5">
         <v>39.770000000000003</v>
       </c>
-    </row>
-    <row r="129" spans="1:19">
+      <c r="T128" s="4">
+        <v>8.31</v>
+      </c>
+      <c r="U128">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21">
       <c r="A129" s="1" t="s">
         <v>127</v>
       </c>
@@ -11224,11 +11981,17 @@
       <c r="R129">
         <v>22.2</v>
       </c>
-      <c r="S129">
+      <c r="S129" s="5">
         <v>81.709999999999994</v>
       </c>
-    </row>
-    <row r="130" spans="1:19">
+      <c r="T129" s="4">
+        <v>7.77</v>
+      </c>
+      <c r="U129">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21">
       <c r="A130" s="1" t="s">
         <v>128</v>
       </c>
@@ -11283,11 +12046,17 @@
       <c r="R130">
         <v>23.5</v>
       </c>
-      <c r="S130">
+      <c r="S130" s="5">
         <v>222.52</v>
       </c>
-    </row>
-    <row r="131" spans="1:19">
+      <c r="T130" s="4">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="U130">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21">
       <c r="A131" s="1" t="s">
         <v>129</v>
       </c>
@@ -11342,11 +12111,17 @@
       <c r="R131">
         <v>22.3</v>
       </c>
-      <c r="S131">
+      <c r="S131" s="5">
         <v>51.89</v>
       </c>
-    </row>
-    <row r="132" spans="1:19">
+      <c r="T131" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U131">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21">
       <c r="A132" s="1" t="s">
         <v>130</v>
       </c>
@@ -11401,11 +12176,17 @@
       <c r="R132">
         <v>24.2</v>
       </c>
-      <c r="S132">
+      <c r="S132" s="5">
         <v>290.39</v>
       </c>
-    </row>
-    <row r="133" spans="1:19">
+      <c r="T132" s="4">
+        <v>7.53</v>
+      </c>
+      <c r="U132">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21">
       <c r="A133" s="1" t="s">
         <v>131</v>
       </c>
@@ -11460,11 +12241,17 @@
       <c r="R133">
         <v>25</v>
       </c>
-      <c r="S133">
+      <c r="S133" s="5">
         <v>14.49</v>
       </c>
-    </row>
-    <row r="134" spans="1:19">
+      <c r="T133" s="4">
+        <v>8.08</v>
+      </c>
+      <c r="U133">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21">
       <c r="A134" s="1" t="s">
         <v>132</v>
       </c>
@@ -11514,16 +12301,22 @@
         <v>490</v>
       </c>
       <c r="Q134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134">
         <v>22.7</v>
       </c>
-      <c r="S134">
+      <c r="S134" s="5">
         <v>14.08</v>
       </c>
-    </row>
-    <row r="135" spans="1:19">
+      <c r="T134" s="4">
+        <v>8.16</v>
+      </c>
+      <c r="U134">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21">
       <c r="A135" s="1" t="s">
         <v>133</v>
       </c>
@@ -11578,11 +12371,17 @@
       <c r="R135">
         <v>22.5</v>
       </c>
-      <c r="S135">
+      <c r="S135" s="5">
         <v>20.58</v>
       </c>
-    </row>
-    <row r="136" spans="1:19">
+      <c r="T135" s="4">
+        <v>7.69</v>
+      </c>
+      <c r="U135">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21">
       <c r="A136" s="1" t="s">
         <v>134</v>
       </c>
@@ -11637,11 +12436,17 @@
       <c r="R136">
         <v>23</v>
       </c>
-      <c r="S136">
+      <c r="S136" s="5">
         <v>49.24</v>
       </c>
-    </row>
-    <row r="137" spans="1:19">
+      <c r="T136" s="4">
+        <v>7.76</v>
+      </c>
+      <c r="U136">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21">
       <c r="A137" s="1" t="s">
         <v>135</v>
       </c>
@@ -11696,11 +12501,17 @@
       <c r="R137">
         <v>24</v>
       </c>
-      <c r="S137">
+      <c r="S137" s="5">
         <v>102.93</v>
       </c>
-    </row>
-    <row r="138" spans="1:19">
+      <c r="T137" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="U137">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21">
       <c r="A138" s="1" t="s">
         <v>136</v>
       </c>
@@ -11755,11 +12566,17 @@
       <c r="R138">
         <v>24.2</v>
       </c>
-      <c r="S138">
+      <c r="S138" s="5">
         <v>201.95</v>
       </c>
-    </row>
-    <row r="139" spans="1:19">
+      <c r="T138" s="4">
+        <v>7.22</v>
+      </c>
+      <c r="U138">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -11814,11 +12631,17 @@
       <c r="R139">
         <v>19.899999999999999</v>
       </c>
-      <c r="S139">
+      <c r="S139" s="5">
         <v>1423.93</v>
       </c>
-    </row>
-    <row r="140" spans="1:19">
+      <c r="T139" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U139">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21">
       <c r="A140" s="1" t="s">
         <v>138</v>
       </c>
@@ -11873,11 +12696,17 @@
       <c r="R140">
         <v>19.899999999999999</v>
       </c>
-      <c r="S140">
+      <c r="S140" s="5">
         <v>1423.93</v>
       </c>
-    </row>
-    <row r="141" spans="1:19">
+      <c r="T140" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U140">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21">
       <c r="A141" s="1" t="s">
         <v>139</v>
       </c>
@@ -11932,11 +12761,17 @@
       <c r="R141">
         <v>19.3</v>
       </c>
-      <c r="S141">
+      <c r="S141" s="5">
         <v>1223.92</v>
       </c>
-    </row>
-    <row r="142" spans="1:19">
+      <c r="T141" s="4">
+        <v>7.97</v>
+      </c>
+      <c r="U141">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21">
       <c r="A142" s="1" t="s">
         <v>140</v>
       </c>
@@ -11991,11 +12826,17 @@
       <c r="R142">
         <v>15.1</v>
       </c>
-      <c r="S142">
+      <c r="S142" s="5">
         <v>3.35</v>
       </c>
-    </row>
-    <row r="143" spans="1:19">
+      <c r="T142" s="4">
+        <v>7.86</v>
+      </c>
+      <c r="U142">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21">
       <c r="A143" s="1" t="s">
         <v>141</v>
       </c>
@@ -12050,11 +12891,17 @@
       <c r="R143">
         <v>18.5</v>
       </c>
-      <c r="S143">
+      <c r="S143" s="5">
         <v>531.13</v>
       </c>
-    </row>
-    <row r="144" spans="1:19">
+      <c r="T143" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="U143">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21">
       <c r="A144" s="1" t="s">
         <v>142</v>
       </c>
@@ -12109,11 +12956,17 @@
       <c r="R144">
         <v>19.2</v>
       </c>
-      <c r="S144">
+      <c r="S144" s="5">
         <v>354.6</v>
       </c>
-    </row>
-    <row r="145" spans="1:19">
+      <c r="T144" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U144">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21">
       <c r="A145" s="1" t="s">
         <v>143</v>
       </c>
@@ -12168,11 +13021,17 @@
       <c r="R145">
         <v>17.399999999999999</v>
       </c>
-      <c r="S145">
+      <c r="S145" s="5">
         <v>1241.6400000000001</v>
       </c>
-    </row>
-    <row r="146" spans="1:19">
+      <c r="T145" s="4">
+        <v>7.75</v>
+      </c>
+      <c r="U145">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21">
       <c r="A146" s="1" t="s">
         <v>144</v>
       </c>
@@ -12227,11 +13086,17 @@
       <c r="R146">
         <v>19.5</v>
       </c>
-      <c r="S146">
+      <c r="S146" s="5">
         <v>57.64</v>
       </c>
-    </row>
-    <row r="147" spans="1:19">
+      <c r="T146" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U146">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21">
       <c r="A147" s="1" t="s">
         <v>145</v>
       </c>
@@ -12286,11 +13151,17 @@
       <c r="R147">
         <v>17</v>
       </c>
-      <c r="S147">
+      <c r="S147" s="5">
         <v>608.97</v>
       </c>
-    </row>
-    <row r="148" spans="1:19">
+      <c r="T147" s="4">
+        <v>7.73</v>
+      </c>
+      <c r="U147">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21">
       <c r="A148" s="1" t="s">
         <v>146</v>
       </c>
@@ -12345,11 +13216,17 @@
       <c r="R148">
         <v>17</v>
       </c>
-      <c r="S148">
+      <c r="S148" s="5">
         <v>102.12</v>
       </c>
-    </row>
-    <row r="149" spans="1:19">
+      <c r="T148" s="4">
+        <v>7.89</v>
+      </c>
+      <c r="U148">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21">
       <c r="A149" s="1" t="s">
         <v>147</v>
       </c>
@@ -12404,11 +13281,17 @@
       <c r="R149">
         <v>16.399999999999999</v>
       </c>
-      <c r="S149">
+      <c r="S149" s="5">
         <v>275.95999999999998</v>
       </c>
-    </row>
-    <row r="150" spans="1:19">
+      <c r="T149" s="4">
+        <v>8.01</v>
+      </c>
+      <c r="U149">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21">
       <c r="A150" s="1" t="s">
         <v>148</v>
       </c>
@@ -12463,11 +13346,17 @@
       <c r="R150">
         <v>16.7</v>
       </c>
-      <c r="S150">
+      <c r="S150" s="5">
         <v>108.81</v>
       </c>
-    </row>
-    <row r="151" spans="1:19">
+      <c r="T150" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U150">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21">
       <c r="A151" s="1" t="s">
         <v>149</v>
       </c>
@@ -12522,11 +13411,17 @@
       <c r="R151">
         <v>16.7</v>
       </c>
-      <c r="S151">
+      <c r="S151" s="5">
         <v>108.81</v>
       </c>
-    </row>
-    <row r="152" spans="1:19">
+      <c r="T151" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U151">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21">
       <c r="A152" s="1" t="s">
         <v>150</v>
       </c>
@@ -12581,11 +13476,17 @@
       <c r="R152">
         <v>25.2</v>
       </c>
-      <c r="S152">
+      <c r="S152" s="5">
         <v>2760.41</v>
       </c>
-    </row>
-    <row r="153" spans="1:19">
+      <c r="T152" s="4">
+        <v>7.39</v>
+      </c>
+      <c r="U152">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21">
       <c r="A153" s="1" t="s">
         <v>151</v>
       </c>
@@ -12640,11 +13541,17 @@
       <c r="R153">
         <v>24.1</v>
       </c>
-      <c r="S153">
+      <c r="S153" s="5">
         <v>434.63</v>
       </c>
-    </row>
-    <row r="154" spans="1:19">
+      <c r="T153" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="U153">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21">
       <c r="A154" s="1" t="s">
         <v>152</v>
       </c>
@@ -12699,11 +13606,17 @@
       <c r="R154">
         <v>24.6</v>
       </c>
-      <c r="S154">
+      <c r="S154" s="5">
         <v>366.8</v>
       </c>
-    </row>
-    <row r="155" spans="1:19">
+      <c r="T154" s="4">
+        <v>7.24</v>
+      </c>
+      <c r="U154">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21">
       <c r="A155" s="1" t="s">
         <v>153</v>
       </c>
@@ -12758,11 +13671,17 @@
       <c r="R155">
         <v>24</v>
       </c>
-      <c r="S155">
+      <c r="S155" s="5">
         <v>185.33</v>
       </c>
-    </row>
-    <row r="156" spans="1:19">
+      <c r="T155" s="4">
+        <v>7.51</v>
+      </c>
+      <c r="U155">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21">
       <c r="A156" s="1" t="s">
         <v>154</v>
       </c>
@@ -12817,11 +13736,17 @@
       <c r="R156">
         <v>24.4</v>
       </c>
-      <c r="S156">
+      <c r="S156" s="5">
         <v>163.65</v>
       </c>
-    </row>
-    <row r="157" spans="1:19">
+      <c r="T156" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U156">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21">
       <c r="A157" s="1" t="s">
         <v>155</v>
       </c>
@@ -12876,11 +13801,17 @@
       <c r="R157">
         <v>23.6</v>
       </c>
-      <c r="S157">
+      <c r="S157" s="5">
         <v>173.02</v>
       </c>
-    </row>
-    <row r="158" spans="1:19">
+      <c r="T157" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="U157">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21">
       <c r="A158" s="1" t="s">
         <v>156</v>
       </c>
@@ -12935,11 +13866,17 @@
       <c r="R158">
         <v>26</v>
       </c>
-      <c r="S158">
+      <c r="S158" s="5">
         <v>291.88</v>
       </c>
-    </row>
-    <row r="159" spans="1:19">
+      <c r="T158" s="4">
+        <v>7.38</v>
+      </c>
+      <c r="U158">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21">
       <c r="A159" s="1" t="s">
         <v>157</v>
       </c>
@@ -12994,11 +13931,17 @@
       <c r="R159">
         <v>25.2</v>
       </c>
-      <c r="S159">
+      <c r="S159" s="5">
         <v>407.21</v>
       </c>
-    </row>
-    <row r="160" spans="1:19">
+      <c r="T159" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U159">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21">
       <c r="A160" s="1" t="s">
         <v>158</v>
       </c>
@@ -13053,11 +13996,17 @@
       <c r="R160">
         <v>25.1</v>
       </c>
-      <c r="S160">
+      <c r="S160" s="5">
         <v>737.9</v>
       </c>
-    </row>
-    <row r="161" spans="1:19">
+      <c r="T160" s="4">
+        <v>7.65</v>
+      </c>
+      <c r="U160">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161" spans="1:21">
       <c r="A161" s="1" t="s">
         <v>159</v>
       </c>
@@ -13112,11 +14061,17 @@
       <c r="R161">
         <v>25.1</v>
       </c>
-      <c r="S161">
+      <c r="S161" s="5">
         <v>737.9</v>
       </c>
-    </row>
-    <row r="162" spans="1:19">
+      <c r="T161" s="4">
+        <v>7.65</v>
+      </c>
+      <c r="U161">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162" spans="1:21">
       <c r="A162" s="1" t="s">
         <v>160</v>
       </c>
@@ -13171,11 +14126,17 @@
       <c r="R162">
         <v>27.6</v>
       </c>
-      <c r="S162">
+      <c r="S162" s="5">
         <v>89.84</v>
       </c>
-    </row>
-    <row r="163" spans="1:19">
+      <c r="T162" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="U162">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="163" spans="1:21">
       <c r="A163" s="1" t="s">
         <v>161</v>
       </c>
@@ -13230,11 +14191,17 @@
       <c r="R163">
         <v>26.6</v>
       </c>
-      <c r="S163">
+      <c r="S163" s="5">
         <v>332.43</v>
       </c>
-    </row>
-    <row r="164" spans="1:19">
+      <c r="T163" s="4">
+        <v>7.74</v>
+      </c>
+      <c r="U163">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21">
       <c r="A164" s="1" t="s">
         <v>162</v>
       </c>
@@ -13289,11 +14256,17 @@
       <c r="R164">
         <v>27.3</v>
       </c>
-      <c r="S164">
+      <c r="S164" s="5">
         <v>143.62</v>
       </c>
-    </row>
-    <row r="165" spans="1:19">
+      <c r="T164" s="4">
+        <v>7.54</v>
+      </c>
+      <c r="U164">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21">
       <c r="A165" s="1" t="s">
         <v>163</v>
       </c>
@@ -13348,11 +14321,17 @@
       <c r="R165">
         <v>27</v>
       </c>
-      <c r="S165">
+      <c r="S165" s="5">
         <v>40.840000000000003</v>
       </c>
-    </row>
-    <row r="166" spans="1:19">
+      <c r="T165" s="4">
+        <v>7.42</v>
+      </c>
+      <c r="U165">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21">
       <c r="A166" s="1" t="s">
         <v>164</v>
       </c>
@@ -13407,11 +14386,17 @@
       <c r="R166">
         <v>23</v>
       </c>
-      <c r="S166">
+      <c r="S166" s="5">
         <v>5.86</v>
       </c>
-    </row>
-    <row r="167" spans="1:19">
+      <c r="T166" s="4">
+        <v>7.34</v>
+      </c>
+      <c r="U166">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21">
       <c r="A167" s="1" t="s">
         <v>165</v>
       </c>
@@ -13466,11 +14451,17 @@
       <c r="R167">
         <v>22.2</v>
       </c>
-      <c r="S167">
+      <c r="S167" s="5">
         <v>83.29</v>
       </c>
-    </row>
-    <row r="168" spans="1:19">
+      <c r="T167" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="U167">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21">
       <c r="A168" s="1" t="s">
         <v>166</v>
       </c>
@@ -13525,11 +14516,17 @@
       <c r="R168">
         <v>21.5</v>
       </c>
-      <c r="S168">
+      <c r="S168" s="5">
         <v>46.08</v>
       </c>
-    </row>
-    <row r="169" spans="1:19">
+      <c r="T168" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U168">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21">
       <c r="A169" s="1" t="s">
         <v>167</v>
       </c>
@@ -13584,11 +14581,17 @@
       <c r="R169">
         <v>24.3</v>
       </c>
-      <c r="S169">
+      <c r="S169" s="5">
         <v>1531.11</v>
       </c>
-    </row>
-    <row r="170" spans="1:19">
+      <c r="T169" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="U169">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21">
       <c r="A170" s="1" t="s">
         <v>168</v>
       </c>
@@ -13643,11 +14646,17 @@
       <c r="R170">
         <v>25.5</v>
       </c>
-      <c r="S170">
+      <c r="S170" s="5">
         <v>21.16</v>
       </c>
-    </row>
-    <row r="171" spans="1:19">
+      <c r="T170" s="4">
+        <v>8.8800000000000008</v>
+      </c>
+      <c r="U170">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21">
       <c r="A171" s="1" t="s">
         <v>169</v>
       </c>
@@ -13702,11 +14711,17 @@
       <c r="R171">
         <v>24</v>
       </c>
-      <c r="S171">
+      <c r="S171" s="5">
         <v>144.44</v>
       </c>
-    </row>
-    <row r="172" spans="1:19">
+      <c r="T171" s="4">
+        <v>7.83</v>
+      </c>
+      <c r="U171">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21">
       <c r="A172" s="1" t="s">
         <v>170</v>
       </c>
@@ -13761,11 +14776,17 @@
       <c r="R172">
         <v>25.4</v>
       </c>
-      <c r="S172">
+      <c r="S172" s="5">
         <v>13.84</v>
       </c>
-    </row>
-    <row r="173" spans="1:19">
+      <c r="T172" s="4">
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="U172">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21">
       <c r="A173" s="1" t="s">
         <v>171</v>
       </c>
@@ -13820,11 +14841,17 @@
       <c r="R173">
         <v>22.4</v>
       </c>
-      <c r="S173">
+      <c r="S173" s="5">
         <v>11.33</v>
       </c>
-    </row>
-    <row r="174" spans="1:19">
+      <c r="T173" s="4">
+        <v>7.81</v>
+      </c>
+      <c r="U173">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21">
       <c r="A174" s="1" t="s">
         <v>172</v>
       </c>
@@ -13879,11 +14906,17 @@
       <c r="R174">
         <v>24.3</v>
       </c>
-      <c r="S174">
+      <c r="S174" s="5">
         <v>547.32000000000005</v>
       </c>
-    </row>
-    <row r="175" spans="1:19">
+      <c r="T174" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="U174">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="175" spans="1:21">
       <c r="A175" s="1" t="s">
         <v>173</v>
       </c>
@@ -13938,11 +14971,17 @@
       <c r="R175">
         <v>22.5</v>
       </c>
-      <c r="S175">
+      <c r="S175" s="5">
         <v>71.66</v>
       </c>
-    </row>
-    <row r="176" spans="1:19">
+      <c r="T175" s="4">
+        <v>7.57</v>
+      </c>
+      <c r="U175">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="176" spans="1:21">
       <c r="A176" s="1" t="s">
         <v>174</v>
       </c>
@@ -13997,11 +15036,17 @@
       <c r="R176">
         <v>23</v>
       </c>
-      <c r="S176">
+      <c r="S176" s="5">
         <v>24.27</v>
       </c>
-    </row>
-    <row r="177" spans="1:19">
+      <c r="T176" s="4">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="U176">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="177" spans="1:21">
       <c r="A177" s="1" t="s">
         <v>175</v>
       </c>
@@ -14056,11 +15101,17 @@
       <c r="R177">
         <v>22.6</v>
       </c>
-      <c r="S177">
+      <c r="S177" s="5">
         <v>48.47</v>
       </c>
-    </row>
-    <row r="178" spans="1:19">
+      <c r="T177" s="4">
+        <v>7.75</v>
+      </c>
+      <c r="U177">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="178" spans="1:21">
       <c r="A178" s="1" t="s">
         <v>176</v>
       </c>
@@ -14115,11 +15166,17 @@
       <c r="R178">
         <v>23.7</v>
       </c>
-      <c r="S178">
+      <c r="S178" s="5">
         <v>629.62</v>
       </c>
-    </row>
-    <row r="179" spans="1:19">
+      <c r="T178" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="U178">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="179" spans="1:21">
       <c r="A179" s="1" t="s">
         <v>177</v>
       </c>
@@ -14174,11 +15231,17 @@
       <c r="R179">
         <v>23.6</v>
       </c>
-      <c r="S179">
+      <c r="S179" s="5">
         <v>133.06</v>
       </c>
-    </row>
-    <row r="180" spans="1:19">
+      <c r="T179" s="4">
+        <v>7.48</v>
+      </c>
+      <c r="U179">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="180" spans="1:21">
       <c r="A180" s="1" t="s">
         <v>178</v>
       </c>
@@ -14233,11 +15296,17 @@
       <c r="R180">
         <v>23.8</v>
       </c>
-      <c r="S180">
+      <c r="S180" s="5">
         <v>9.56</v>
       </c>
-    </row>
-    <row r="181" spans="1:19">
+      <c r="T180" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U180">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="181" spans="1:21">
       <c r="A181" s="1" t="s">
         <v>179</v>
       </c>
@@ -14292,11 +15361,17 @@
       <c r="R181">
         <v>23.6</v>
       </c>
-      <c r="S181">
+      <c r="S181" s="5">
         <v>23.53</v>
       </c>
-    </row>
-    <row r="182" spans="1:19">
+      <c r="T181" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="U181">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="182" spans="1:21">
       <c r="A182" s="1" t="s">
         <v>180</v>
       </c>
@@ -14351,11 +15426,17 @@
       <c r="R182">
         <v>22.5</v>
       </c>
-      <c r="S182">
+      <c r="S182" s="5">
         <v>8.5399999999999991</v>
       </c>
-    </row>
-    <row r="183" spans="1:19">
+      <c r="T182" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="U182">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="183" spans="1:21">
       <c r="A183" s="1" t="s">
         <v>181</v>
       </c>
@@ -14410,11 +15491,17 @@
       <c r="R183">
         <v>21.5</v>
       </c>
-      <c r="S183">
+      <c r="S183" s="5">
         <v>8.6199999999999992</v>
       </c>
-    </row>
-    <row r="184" spans="1:19">
+      <c r="T183" s="4">
+        <v>7.73</v>
+      </c>
+      <c r="U183">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="184" spans="1:21">
       <c r="A184" s="1" t="s">
         <v>182</v>
       </c>
@@ -14469,11 +15556,17 @@
       <c r="R184">
         <v>22.8</v>
       </c>
-      <c r="S184">
+      <c r="S184" s="5">
         <v>3.02</v>
       </c>
-    </row>
-    <row r="185" spans="1:19">
+      <c r="T184" s="4">
+        <v>9.01</v>
+      </c>
+      <c r="U184">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="185" spans="1:21">
       <c r="A185" s="1" t="s">
         <v>183</v>
       </c>
@@ -14528,11 +15621,17 @@
       <c r="R185">
         <v>24.8</v>
       </c>
-      <c r="S185">
+      <c r="S185" s="5">
         <v>337.78</v>
       </c>
-    </row>
-    <row r="186" spans="1:19">
+      <c r="T185" s="4">
+        <v>7.68</v>
+      </c>
+      <c r="U185">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:21">
       <c r="A186" s="1" t="s">
         <v>184</v>
       </c>
@@ -14587,11 +15686,17 @@
       <c r="R186">
         <v>21.8</v>
       </c>
-      <c r="S186">
+      <c r="S186" s="5">
         <v>30.46</v>
       </c>
-    </row>
-    <row r="187" spans="1:19">
+      <c r="T186" s="4">
+        <v>7.71</v>
+      </c>
+      <c r="U186">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="187" spans="1:21">
       <c r="A187" s="1" t="s">
         <v>185</v>
       </c>
@@ -14646,11 +15751,17 @@
       <c r="R187">
         <v>21.4</v>
       </c>
-      <c r="S187">
+      <c r="S187" s="5">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="188" spans="1:19">
+      <c r="T187" s="4">
+        <v>7.25</v>
+      </c>
+      <c r="U187">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="188" spans="1:21">
       <c r="A188" s="1" t="s">
         <v>186</v>
       </c>
@@ -14705,11 +15816,17 @@
       <c r="R188">
         <v>23.7</v>
       </c>
-      <c r="S188">
+      <c r="S188" s="5">
         <v>32.86</v>
       </c>
-    </row>
-    <row r="189" spans="1:19">
+      <c r="T188" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="U188">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="189" spans="1:21">
       <c r="A189" s="1" t="s">
         <v>187</v>
       </c>
@@ -14764,11 +15881,17 @@
       <c r="R189">
         <v>25.3</v>
       </c>
-      <c r="S189">
+      <c r="S189" s="5">
         <v>307.20999999999998</v>
       </c>
-    </row>
-    <row r="190" spans="1:19">
+      <c r="T189" s="4">
+        <v>7.28</v>
+      </c>
+      <c r="U189">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="190" spans="1:21">
       <c r="A190" s="1" t="s">
         <v>188</v>
       </c>
@@ -14823,11 +15946,17 @@
       <c r="R190">
         <v>19.8</v>
       </c>
-      <c r="S190">
+      <c r="S190" s="5">
         <v>46.79</v>
       </c>
-    </row>
-    <row r="191" spans="1:19">
+      <c r="T190" s="4">
+        <v>7.41</v>
+      </c>
+      <c r="U190">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="191" spans="1:21">
       <c r="A191" s="1" t="s">
         <v>189</v>
       </c>
@@ -14882,11 +16011,17 @@
       <c r="R191">
         <v>19.8</v>
       </c>
-      <c r="S191">
+      <c r="S191" s="5">
         <v>30.3</v>
       </c>
-    </row>
-    <row r="192" spans="1:19">
+      <c r="T191" s="4">
+        <v>7.62</v>
+      </c>
+      <c r="U191">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="192" spans="1:21">
       <c r="A192" s="1" t="s">
         <v>190</v>
       </c>
@@ -14941,11 +16076,17 @@
       <c r="R192">
         <v>19.8</v>
       </c>
-      <c r="S192">
+      <c r="S192" s="5">
         <v>30.3</v>
       </c>
-    </row>
-    <row r="193" spans="1:19">
+      <c r="T192" s="4">
+        <v>7.62</v>
+      </c>
+      <c r="U192">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="193" spans="1:21">
       <c r="A193" s="1" t="s">
         <v>191</v>
       </c>
@@ -14956,7 +16097,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="194" spans="1:19">
+    <row r="194" spans="1:21">
       <c r="A194" s="1" t="s">
         <v>192</v>
       </c>
@@ -14967,7 +16108,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="195" spans="1:19">
+    <row r="195" spans="1:21">
       <c r="A195" s="1" t="s">
         <v>193</v>
       </c>
@@ -14978,7 +16119,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="196" spans="1:19">
+    <row r="196" spans="1:21">
       <c r="A196" s="1" t="s">
         <v>194</v>
       </c>
@@ -14989,7 +16130,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="197" spans="1:19">
+    <row r="197" spans="1:21">
       <c r="A197" s="1" t="s">
         <v>195</v>
       </c>
@@ -15000,7 +16141,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="198" spans="1:19">
+    <row r="198" spans="1:21">
       <c r="A198" s="1" t="s">
         <v>274</v>
       </c>
@@ -15055,11 +16196,17 @@
       <c r="R198">
         <v>25.8</v>
       </c>
-      <c r="S198">
+      <c r="S198" s="5">
         <v>1936.15</v>
       </c>
-    </row>
-    <row r="199" spans="1:19">
+      <c r="T198" s="4">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="U198">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199" spans="1:21">
       <c r="A199" s="2" t="s">
         <v>275</v>
       </c>
@@ -15114,11 +16261,17 @@
       <c r="R199">
         <v>25.8</v>
       </c>
-      <c r="S199">
+      <c r="S199" s="5">
         <v>1936.15</v>
       </c>
-    </row>
-    <row r="200" spans="1:19">
+      <c r="T199" s="4">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="U199">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="200" spans="1:21">
       <c r="A200" s="1" t="s">
         <v>297</v>
       </c>
@@ -15173,11 +16326,17 @@
       <c r="R200">
         <v>23.2</v>
       </c>
-      <c r="S200">
+      <c r="S200" s="5">
         <v>428.55</v>
       </c>
-    </row>
-    <row r="201" spans="1:19">
+      <c r="T200" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="U200">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:21">
       <c r="A201" s="1" t="s">
         <v>296</v>
       </c>
@@ -15232,11 +16391,17 @@
       <c r="R201">
         <v>23.2</v>
       </c>
-      <c r="S201">
+      <c r="S201" s="5">
         <v>428.55</v>
       </c>
-    </row>
-    <row r="202" spans="1:19">
+      <c r="T201" s="4">
+        <v>7.94</v>
+      </c>
+      <c r="U201">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="202" spans="1:21">
       <c r="A202" s="1" t="s">
         <v>295</v>
       </c>
@@ -15291,11 +16456,17 @@
       <c r="R202">
         <v>25.1</v>
       </c>
-      <c r="S202">
+      <c r="S202" s="5">
         <v>948.37</v>
       </c>
-    </row>
-    <row r="203" spans="1:19">
+      <c r="T202" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U202">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="203" spans="1:21">
       <c r="A203" s="1" t="s">
         <v>294</v>
       </c>
@@ -15350,11 +16521,17 @@
       <c r="R203">
         <v>25.1</v>
       </c>
-      <c r="S203">
+      <c r="S203" s="5">
         <v>948.37</v>
       </c>
-    </row>
-    <row r="204" spans="1:19">
+      <c r="T203" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U203">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="204" spans="1:21">
       <c r="A204" s="1" t="s">
         <v>293</v>
       </c>
@@ -15409,11 +16586,17 @@
       <c r="R204">
         <v>24.8</v>
       </c>
-      <c r="S204">
+      <c r="S204" s="5">
         <v>87.9</v>
       </c>
-    </row>
-    <row r="205" spans="1:19">
+      <c r="T204" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="U204">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="205" spans="1:21">
       <c r="A205" s="1" t="s">
         <v>292</v>
       </c>
@@ -15468,11 +16651,17 @@
       <c r="R205">
         <v>24.8</v>
       </c>
-      <c r="S205">
+      <c r="S205" s="5">
         <v>87.9</v>
       </c>
-    </row>
-    <row r="206" spans="1:19">
+      <c r="T205" s="4">
+        <v>7.6</v>
+      </c>
+      <c r="U205">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="206" spans="1:21">
       <c r="A206" s="1" t="s">
         <v>291</v>
       </c>
@@ -15527,11 +16716,17 @@
       <c r="R206">
         <v>22.2</v>
       </c>
-      <c r="S206">
+      <c r="S206" s="5">
         <v>823.3</v>
       </c>
-    </row>
-    <row r="207" spans="1:19">
+      <c r="T206" s="4">
+        <v>7.95</v>
+      </c>
+      <c r="U206">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="207" spans="1:21">
       <c r="A207" s="1" t="s">
         <v>290</v>
       </c>
@@ -15586,11 +16781,17 @@
       <c r="R207">
         <v>22.2</v>
       </c>
-      <c r="S207">
+      <c r="S207" s="5">
         <v>823.3</v>
       </c>
-    </row>
-    <row r="208" spans="1:19">
+      <c r="T207" s="4">
+        <v>7.95</v>
+      </c>
+      <c r="U207">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="208" spans="1:21">
       <c r="A208" s="1" t="s">
         <v>289</v>
       </c>
@@ -15645,11 +16846,17 @@
       <c r="R208">
         <v>19.5</v>
       </c>
-      <c r="S208">
+      <c r="S208" s="5">
         <v>925</v>
       </c>
-    </row>
-    <row r="209" spans="1:19">
+      <c r="T208" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="U208">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="209" spans="1:21">
       <c r="A209" s="1" t="s">
         <v>288</v>
       </c>
@@ -15704,11 +16911,17 @@
       <c r="R209">
         <v>19.5</v>
       </c>
-      <c r="S209">
+      <c r="S209" s="5">
         <v>925</v>
       </c>
-    </row>
-    <row r="210" spans="1:19">
+      <c r="T209" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="U209">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="210" spans="1:21">
       <c r="A210" s="1" t="s">
         <v>287</v>
       </c>
@@ -15763,11 +16976,17 @@
       <c r="R210">
         <v>20.8</v>
       </c>
-      <c r="S210">
+      <c r="S210" s="5">
         <v>653.33000000000004</v>
       </c>
-    </row>
-    <row r="211" spans="1:19">
+      <c r="T210" s="4">
+        <v>7.97</v>
+      </c>
+      <c r="U210">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="211" spans="1:21">
       <c r="A211" s="1" t="s">
         <v>286</v>
       </c>
@@ -15822,11 +17041,17 @@
       <c r="R211">
         <v>20.8</v>
       </c>
-      <c r="S211">
+      <c r="S211" s="5">
         <v>653.33000000000004</v>
       </c>
-    </row>
-    <row r="212" spans="1:19">
+      <c r="T211" s="4">
+        <v>7.97</v>
+      </c>
+      <c r="U211">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="212" spans="1:21">
       <c r="A212" s="1" t="s">
         <v>285</v>
       </c>
@@ -15881,11 +17106,17 @@
       <c r="R212">
         <v>22.3</v>
       </c>
-      <c r="S212">
+      <c r="S212" s="5">
         <v>106.86</v>
       </c>
-    </row>
-    <row r="213" spans="1:19">
+      <c r="T212" s="4">
+        <v>8.07</v>
+      </c>
+      <c r="U212">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="213" spans="1:21">
       <c r="A213" s="1" t="s">
         <v>284</v>
       </c>
@@ -15940,11 +17171,17 @@
       <c r="R213">
         <v>22.3</v>
       </c>
-      <c r="S213">
+      <c r="S213" s="5">
         <v>106.86</v>
       </c>
-    </row>
-    <row r="214" spans="1:19">
+      <c r="T213" s="4">
+        <v>8.07</v>
+      </c>
+      <c r="U213">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="214" spans="1:21">
       <c r="A214" s="1" t="s">
         <v>283</v>
       </c>
@@ -15999,11 +17236,17 @@
       <c r="R214">
         <v>22.1</v>
       </c>
-      <c r="S214">
+      <c r="S214" s="5">
         <v>138.44999999999999</v>
       </c>
-    </row>
-    <row r="215" spans="1:19">
+      <c r="T214" s="4">
+        <v>7.69</v>
+      </c>
+      <c r="U214">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="215" spans="1:21">
       <c r="A215" s="1" t="s">
         <v>282</v>
       </c>
@@ -16058,11 +17301,17 @@
       <c r="R215">
         <v>22.1</v>
       </c>
-      <c r="S215">
+      <c r="S215" s="5">
         <v>138.44999999999999</v>
       </c>
-    </row>
-    <row r="216" spans="1:19">
+      <c r="T215" s="4">
+        <v>7.69</v>
+      </c>
+      <c r="U215">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="216" spans="1:21">
       <c r="A216" s="1" t="s">
         <v>281</v>
       </c>
@@ -16117,11 +17366,17 @@
       <c r="R216">
         <v>22.6</v>
       </c>
-      <c r="S216">
+      <c r="S216" s="5">
         <v>445.17</v>
       </c>
-    </row>
-    <row r="217" spans="1:19">
+      <c r="T216" s="4">
+        <v>8.06</v>
+      </c>
+      <c r="U216">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="217" spans="1:21">
       <c r="A217" s="1" t="s">
         <v>280</v>
       </c>
@@ -16176,11 +17431,17 @@
       <c r="R217">
         <v>22.6</v>
       </c>
-      <c r="S217">
+      <c r="S217" s="5">
         <v>445.17</v>
       </c>
-    </row>
-    <row r="218" spans="1:19">
+      <c r="T217" s="4">
+        <v>8.06</v>
+      </c>
+      <c r="U217">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="218" spans="1:21">
       <c r="A218" s="1" t="s">
         <v>279</v>
       </c>
@@ -16235,11 +17496,17 @@
       <c r="R218">
         <v>23</v>
       </c>
-      <c r="S218">
+      <c r="S218" s="5">
         <v>813.79</v>
       </c>
-    </row>
-    <row r="219" spans="1:19">
+      <c r="T218" s="4">
+        <v>7.67</v>
+      </c>
+      <c r="U218">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="219" spans="1:21">
       <c r="A219" s="1" t="s">
         <v>278</v>
       </c>
@@ -16294,11 +17561,17 @@
       <c r="R219">
         <v>23</v>
       </c>
-      <c r="S219">
+      <c r="S219" s="5">
         <v>813.79</v>
       </c>
-    </row>
-    <row r="220" spans="1:19">
+      <c r="T219" s="4">
+        <v>7.67</v>
+      </c>
+      <c r="U219">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="220" spans="1:21">
       <c r="A220" s="1" t="s">
         <v>277</v>
       </c>
@@ -16353,11 +17626,17 @@
       <c r="R220">
         <v>21.6</v>
       </c>
-      <c r="S220">
+      <c r="S220" s="5">
         <v>541.14</v>
       </c>
-    </row>
-    <row r="221" spans="1:19">
+      <c r="T220" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U220">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="221" spans="1:21">
       <c r="A221" s="1" t="s">
         <v>276</v>
       </c>
@@ -16412,11 +17691,17 @@
       <c r="R221">
         <v>21.6</v>
       </c>
-      <c r="S221">
+      <c r="S221" s="5">
         <v>541.14</v>
       </c>
-    </row>
-    <row r="222" spans="1:19">
+      <c r="T221" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U221">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="222" spans="1:21">
       <c r="A222" s="1" t="s">
         <v>196</v>
       </c>
@@ -16471,11 +17756,17 @@
       <c r="R222">
         <v>23.3</v>
       </c>
-      <c r="S222">
+      <c r="S222" s="5">
         <v>1103.4000000000001</v>
       </c>
-    </row>
-    <row r="223" spans="1:19">
+      <c r="T222" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U222">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="223" spans="1:21">
       <c r="A223" s="1" t="s">
         <v>197</v>
       </c>
@@ -16530,11 +17821,17 @@
       <c r="R223">
         <v>23.3</v>
       </c>
-      <c r="S223">
+      <c r="S223" s="5">
         <v>1103.4000000000001</v>
       </c>
-    </row>
-    <row r="224" spans="1:19">
+      <c r="T223" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U223">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="224" spans="1:21">
       <c r="A224" s="1" t="s">
         <v>198</v>
       </c>
@@ -16589,11 +17886,17 @@
       <c r="R224">
         <v>24.5</v>
       </c>
-      <c r="S224">
+      <c r="S224" s="5">
         <v>766.02</v>
       </c>
-    </row>
-    <row r="225" spans="1:19">
+      <c r="T224" s="4">
+        <v>8</v>
+      </c>
+      <c r="U224">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="225" spans="1:21">
       <c r="A225" s="1" t="s">
         <v>199</v>
       </c>
@@ -16648,11 +17951,17 @@
       <c r="R225">
         <v>24.5</v>
       </c>
-      <c r="S225">
+      <c r="S225" s="5">
         <v>766.02</v>
       </c>
-    </row>
-    <row r="226" spans="1:19">
+      <c r="T225" s="4">
+        <v>8</v>
+      </c>
+      <c r="U225">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="226" spans="1:21">
       <c r="A226" s="1" t="s">
         <v>200</v>
       </c>
@@ -16707,11 +18016,17 @@
       <c r="R226">
         <v>25.5</v>
       </c>
-      <c r="S226">
+      <c r="S226" s="5">
         <v>940.72</v>
       </c>
-    </row>
-    <row r="227" spans="1:19">
+      <c r="T226" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U226">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="1:21">
       <c r="A227" s="1" t="s">
         <v>201</v>
       </c>
@@ -16766,11 +18081,17 @@
       <c r="R227">
         <v>25.5</v>
       </c>
-      <c r="S227">
+      <c r="S227" s="5">
         <v>940.72</v>
       </c>
-    </row>
-    <row r="228" spans="1:19">
+      <c r="T227" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U227">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="228" spans="1:21">
       <c r="A228" s="1" t="s">
         <v>202</v>
       </c>
@@ -16825,11 +18146,17 @@
       <c r="R228">
         <v>31.8</v>
       </c>
-      <c r="S228">
+      <c r="S228" s="5">
         <v>1234.1600000000001</v>
       </c>
-    </row>
-    <row r="229" spans="1:19">
+      <c r="T228" s="4">
+        <v>8.42</v>
+      </c>
+      <c r="U228">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="229" spans="1:21">
       <c r="A229" s="1" t="s">
         <v>203</v>
       </c>
@@ -16884,11 +18211,17 @@
       <c r="R229">
         <v>31.8</v>
       </c>
-      <c r="S229">
+      <c r="S229" s="5">
         <v>1234.1600000000001</v>
       </c>
-    </row>
-    <row r="230" spans="1:19">
+      <c r="T229" s="4">
+        <v>8.42</v>
+      </c>
+      <c r="U229">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="230" spans="1:21">
       <c r="A230" s="1" t="s">
         <v>204</v>
       </c>
@@ -16943,11 +18276,17 @@
       <c r="R230">
         <v>27.2</v>
       </c>
-      <c r="S230">
+      <c r="S230" s="5">
         <v>1097.42</v>
       </c>
-    </row>
-    <row r="231" spans="1:19">
+      <c r="T230" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U230">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="231" spans="1:21">
       <c r="A231" s="1" t="s">
         <v>205</v>
       </c>
@@ -17002,11 +18341,17 @@
       <c r="R231">
         <v>27.2</v>
       </c>
-      <c r="S231">
+      <c r="S231" s="5">
         <v>1097.42</v>
       </c>
-    </row>
-    <row r="232" spans="1:19">
+      <c r="T231" s="4">
+        <v>8.02</v>
+      </c>
+      <c r="U231">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="232" spans="1:21">
       <c r="A232" s="1" t="s">
         <v>206</v>
       </c>
@@ -17061,11 +18406,17 @@
       <c r="R232">
         <v>25.3</v>
       </c>
-      <c r="S232">
+      <c r="S232" s="5">
         <v>605.22</v>
       </c>
-    </row>
-    <row r="233" spans="1:19">
+      <c r="T232" s="4">
+        <v>8.17</v>
+      </c>
+      <c r="U232">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="233" spans="1:21">
       <c r="A233" s="1" t="s">
         <v>207</v>
       </c>
@@ -17120,11 +18471,17 @@
       <c r="R233">
         <v>25.3</v>
       </c>
-      <c r="S233">
+      <c r="S233" s="5">
         <v>605.22</v>
       </c>
-    </row>
-    <row r="234" spans="1:19">
+      <c r="T233" s="4">
+        <v>8.17</v>
+      </c>
+      <c r="U233">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="234" spans="1:21">
       <c r="A234" s="1" t="s">
         <v>208</v>
       </c>
@@ -17179,11 +18536,17 @@
       <c r="R234">
         <v>22.4</v>
       </c>
-      <c r="S234">
+      <c r="S234" s="5">
         <v>1596.32</v>
       </c>
-    </row>
-    <row r="235" spans="1:19">
+      <c r="T234" s="4">
+        <v>7.96</v>
+      </c>
+      <c r="U234">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="235" spans="1:21">
       <c r="A235" s="1" t="s">
         <v>209</v>
       </c>
@@ -17238,11 +18601,17 @@
       <c r="R235">
         <v>22.4</v>
       </c>
-      <c r="S235">
+      <c r="S235" s="5">
         <v>1596.32</v>
       </c>
-    </row>
-    <row r="236" spans="1:19">
+      <c r="T235" s="4">
+        <v>7.96</v>
+      </c>
+      <c r="U235">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236" spans="1:21">
       <c r="A236" s="1" t="s">
         <v>210</v>
       </c>
@@ -17297,11 +18666,17 @@
       <c r="R236">
         <v>22.8</v>
       </c>
-      <c r="S236">
+      <c r="S236" s="5">
         <v>243.5</v>
       </c>
-    </row>
-    <row r="237" spans="1:19">
+      <c r="T236" s="4">
+        <v>8.41</v>
+      </c>
+      <c r="U236">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="237" spans="1:21">
       <c r="A237" s="1" t="s">
         <v>211</v>
       </c>
@@ -17356,11 +18731,17 @@
       <c r="R237">
         <v>22.8</v>
       </c>
-      <c r="S237">
+      <c r="S237" s="5">
         <v>243.5</v>
       </c>
-    </row>
-    <row r="238" spans="1:19">
+      <c r="T237" s="4">
+        <v>8.41</v>
+      </c>
+      <c r="U237">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="238" spans="1:21">
       <c r="A238" s="1" t="s">
         <v>212</v>
       </c>
@@ -17415,11 +18796,17 @@
       <c r="R238">
         <v>26</v>
       </c>
-      <c r="S238">
+      <c r="S238" s="5">
         <v>40.840000000000003</v>
       </c>
-    </row>
-    <row r="239" spans="1:19">
+      <c r="T238" s="4">
+        <v>10.02</v>
+      </c>
+      <c r="U238">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="239" spans="1:21">
       <c r="A239" s="1" t="s">
         <v>213</v>
       </c>
@@ -17474,11 +18861,17 @@
       <c r="R239">
         <v>26</v>
       </c>
-      <c r="S239">
+      <c r="S239" s="5">
         <v>40.840000000000003</v>
       </c>
-    </row>
-    <row r="240" spans="1:19">
+      <c r="T239" s="4">
+        <v>10.02</v>
+      </c>
+      <c r="U239">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="240" spans="1:21">
       <c r="A240" s="1" t="s">
         <v>214</v>
       </c>
@@ -17533,11 +18926,17 @@
       <c r="R240">
         <v>25.5</v>
       </c>
-      <c r="S240">
+      <c r="S240" s="5">
         <v>32.11</v>
       </c>
-    </row>
-    <row r="241" spans="1:19">
+      <c r="T240" s="4">
+        <v>9.31</v>
+      </c>
+      <c r="U240">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="241" spans="1:21">
       <c r="A241" s="1" t="s">
         <v>215</v>
       </c>
@@ -17592,11 +18991,17 @@
       <c r="R241">
         <v>25.5</v>
       </c>
-      <c r="S241">
+      <c r="S241" s="5">
         <v>32.11</v>
       </c>
-    </row>
-    <row r="242" spans="1:19">
+      <c r="T241" s="4">
+        <v>9.31</v>
+      </c>
+      <c r="U241">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="242" spans="1:21">
       <c r="A242" s="1" t="s">
         <v>216</v>
       </c>
@@ -17651,11 +19056,17 @@
       <c r="R242">
         <v>26.8</v>
       </c>
-      <c r="S242">
+      <c r="S242" s="5">
         <v>327.61</v>
       </c>
-    </row>
-    <row r="243" spans="1:19">
+      <c r="T242" s="4">
+        <v>8.26</v>
+      </c>
+      <c r="U242">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="243" spans="1:21">
       <c r="A243" s="1" t="s">
         <v>217</v>
       </c>
@@ -17710,11 +19121,17 @@
       <c r="R243">
         <v>26.8</v>
       </c>
-      <c r="S243">
+      <c r="S243" s="5">
         <v>327.61</v>
       </c>
-    </row>
-    <row r="244" spans="1:19">
+      <c r="T243" s="4">
+        <v>8.26</v>
+      </c>
+      <c r="U243">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="244" spans="1:21">
       <c r="A244" s="1" t="s">
         <v>218</v>
       </c>
@@ -17769,11 +19186,17 @@
       <c r="R244">
         <v>24</v>
       </c>
-      <c r="S244">
+      <c r="S244" s="5">
         <v>39.450000000000003</v>
       </c>
-    </row>
-    <row r="245" spans="1:19">
+      <c r="T244" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="U244">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="245" spans="1:21">
       <c r="A245" s="1" t="s">
         <v>219</v>
       </c>
@@ -17828,11 +19251,17 @@
       <c r="R245">
         <v>24</v>
       </c>
-      <c r="S245">
+      <c r="S245" s="5">
         <v>39.450000000000003</v>
       </c>
-    </row>
-    <row r="246" spans="1:19">
+      <c r="T245" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="U245">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="246" spans="1:21">
       <c r="A246" s="1" t="s">
         <v>220</v>
       </c>
@@ -17887,11 +19316,17 @@
       <c r="R246">
         <v>25.1</v>
       </c>
-      <c r="S246">
+      <c r="S246" s="5">
         <v>11.2</v>
       </c>
-    </row>
-    <row r="247" spans="1:19">
+      <c r="T246" s="4">
+        <v>7.64</v>
+      </c>
+      <c r="U246">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="247" spans="1:21">
       <c r="A247" s="1" t="s">
         <v>221</v>
       </c>
@@ -17946,11 +19381,17 @@
       <c r="R247">
         <v>25.1</v>
       </c>
-      <c r="S247">
+      <c r="S247" s="5">
         <v>11.2</v>
       </c>
-    </row>
-    <row r="248" spans="1:19">
+      <c r="T247" s="4">
+        <v>7.64</v>
+      </c>
+      <c r="U247">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="248" spans="1:21">
       <c r="A248" s="1" t="s">
         <v>222</v>
       </c>
@@ -18005,11 +19446,17 @@
       <c r="R248">
         <v>25.2</v>
       </c>
-      <c r="S248">
+      <c r="S248" s="5">
         <v>2760.41</v>
       </c>
-    </row>
-    <row r="249" spans="1:19">
+      <c r="T248" s="4">
+        <v>7.39</v>
+      </c>
+      <c r="U248">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="249" spans="1:21">
       <c r="A249" s="1" t="s">
         <v>223</v>
       </c>
@@ -18064,11 +19511,17 @@
       <c r="R249">
         <v>25.2</v>
       </c>
-      <c r="S249">
+      <c r="S249" s="5">
         <v>2760.41</v>
       </c>
-    </row>
-    <row r="250" spans="1:19">
+      <c r="T249" s="4">
+        <v>7.39</v>
+      </c>
+      <c r="U249">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="250" spans="1:21">
       <c r="A250" s="1" t="s">
         <v>224</v>
       </c>
@@ -18123,11 +19576,17 @@
       <c r="R250">
         <v>27.6</v>
       </c>
-      <c r="S250">
+      <c r="S250" s="5">
         <v>89.84</v>
       </c>
-    </row>
-    <row r="251" spans="1:19">
+      <c r="T250" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="U250">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="251" spans="1:21">
       <c r="A251" s="1" t="s">
         <v>225</v>
       </c>
@@ -18182,11 +19641,17 @@
       <c r="R251">
         <v>27.6</v>
       </c>
-      <c r="S251">
+      <c r="S251" s="5">
         <v>89.84</v>
       </c>
-    </row>
-    <row r="252" spans="1:19">
+      <c r="T251" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="U251">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="252" spans="1:21">
       <c r="A252" s="1" t="s">
         <v>226</v>
       </c>
@@ -18241,11 +19706,17 @@
       <c r="R252">
         <v>26.2</v>
       </c>
-      <c r="S252">
+      <c r="S252" s="5">
         <v>274.68</v>
       </c>
-    </row>
-    <row r="253" spans="1:19">
+      <c r="T252" s="4">
+        <v>7.79</v>
+      </c>
+      <c r="U252">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="253" spans="1:21">
       <c r="A253" s="1" t="s">
         <v>227</v>
       </c>
@@ -18300,11 +19771,17 @@
       <c r="R253">
         <v>26.2</v>
       </c>
-      <c r="S253">
+      <c r="S253" s="5">
         <v>274.68</v>
       </c>
-    </row>
-    <row r="254" spans="1:19">
+      <c r="T253" s="4">
+        <v>7.79</v>
+      </c>
+      <c r="U253">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="254" spans="1:21">
       <c r="A254" s="1" t="s">
         <v>228</v>
       </c>
@@ -18359,11 +19836,17 @@
       <c r="R254">
         <v>23</v>
       </c>
-      <c r="S254">
+      <c r="S254" s="5">
         <v>12.3</v>
       </c>
-    </row>
-    <row r="255" spans="1:19">
+      <c r="T254" s="4">
+        <v>8.25</v>
+      </c>
+      <c r="U254">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="255" spans="1:21">
       <c r="A255" s="1" t="s">
         <v>229</v>
       </c>
@@ -18418,11 +19901,17 @@
       <c r="R255">
         <v>23</v>
       </c>
-      <c r="S255">
+      <c r="S255" s="5">
         <v>12.3</v>
       </c>
-    </row>
-    <row r="256" spans="1:19">
+      <c r="T255" s="4">
+        <v>8.25</v>
+      </c>
+      <c r="U255">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="256" spans="1:21">
       <c r="A256" s="1" t="s">
         <v>230</v>
       </c>
@@ -18477,11 +19966,17 @@
       <c r="R256">
         <v>24.2</v>
       </c>
-      <c r="S256">
+      <c r="S256" s="5">
         <v>329.71</v>
       </c>
-    </row>
-    <row r="257" spans="1:19">
+      <c r="T256" s="4">
+        <v>8.08</v>
+      </c>
+      <c r="U256">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21">
       <c r="A257" s="1" t="s">
         <v>231</v>
       </c>
@@ -18536,11 +20031,17 @@
       <c r="R257">
         <v>24.2</v>
       </c>
-      <c r="S257">
+      <c r="S257" s="5">
         <v>329.71</v>
       </c>
-    </row>
-    <row r="258" spans="1:19">
+      <c r="T257" s="4">
+        <v>8.08</v>
+      </c>
+      <c r="U257">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="258" spans="1:21">
       <c r="A258" s="1" t="s">
         <v>232</v>
       </c>
@@ -18595,11 +20096,17 @@
       <c r="R258">
         <v>23.3</v>
       </c>
-      <c r="S258">
+      <c r="S258" s="5">
         <v>134.52000000000001</v>
       </c>
-    </row>
-    <row r="259" spans="1:19">
+      <c r="T258" s="4">
+        <v>7.98</v>
+      </c>
+      <c r="U258">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="259" spans="1:21">
       <c r="A259" s="1" t="s">
         <v>233</v>
       </c>
@@ -18654,11 +20161,17 @@
       <c r="R259">
         <v>23.3</v>
       </c>
-      <c r="S259">
+      <c r="S259" s="5">
         <v>134.52000000000001</v>
       </c>
-    </row>
-    <row r="260" spans="1:19">
+      <c r="T259" s="4">
+        <v>7.98</v>
+      </c>
+      <c r="U259">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="260" spans="1:21">
       <c r="A260" s="1" t="s">
         <v>234</v>
       </c>
@@ -18713,11 +20226,17 @@
       <c r="R260">
         <v>24.3</v>
       </c>
-      <c r="S260">
+      <c r="S260" s="5">
         <v>22.1</v>
       </c>
-    </row>
-    <row r="261" spans="1:19">
+      <c r="T260" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="U260">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21">
       <c r="A261" s="1" t="s">
         <v>235</v>
       </c>
@@ -18772,11 +20291,17 @@
       <c r="R261">
         <v>24.3</v>
       </c>
-      <c r="S261">
+      <c r="S261" s="5">
         <v>22.1</v>
       </c>
-    </row>
-    <row r="262" spans="1:19">
+      <c r="T261" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="U261">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="262" spans="1:21">
       <c r="A262" s="1" t="s">
         <v>236</v>
       </c>
@@ -18831,11 +20356,17 @@
       <c r="R262">
         <v>19.899999999999999</v>
       </c>
-      <c r="S262">
+      <c r="S262" s="5">
         <v>47.87</v>
       </c>
-    </row>
-    <row r="263" spans="1:19">
+      <c r="T262" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U262">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21">
       <c r="A263" s="1" t="s">
         <v>237</v>
       </c>
@@ -18890,11 +20421,17 @@
       <c r="R263">
         <v>19.899999999999999</v>
       </c>
-      <c r="S263">
+      <c r="S263" s="5">
         <v>47.87</v>
       </c>
-    </row>
-    <row r="264" spans="1:19">
+      <c r="T263" s="4">
+        <v>7.99</v>
+      </c>
+      <c r="U263">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21">
       <c r="A264" s="1" t="s">
         <v>238</v>
       </c>
@@ -18949,11 +20486,17 @@
       <c r="R264">
         <v>24.3</v>
       </c>
-      <c r="S264">
+      <c r="S264" s="5">
         <v>1531.11</v>
       </c>
-    </row>
-    <row r="265" spans="1:19">
+      <c r="T264" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="U264">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="265" spans="1:21">
       <c r="A265" s="1" t="s">
         <v>239</v>
       </c>
@@ -19008,11 +20551,17 @@
       <c r="R265">
         <v>24.3</v>
       </c>
-      <c r="S265">
+      <c r="S265" s="5">
         <v>1531.11</v>
       </c>
-    </row>
-    <row r="266" spans="1:19">
+      <c r="T265" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="U265">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="266" spans="1:21">
       <c r="A266" s="1" t="s">
         <v>240</v>
       </c>
@@ -19067,11 +20616,17 @@
       <c r="R266">
         <v>23.7</v>
       </c>
-      <c r="S266">
+      <c r="S266" s="5">
         <v>629.62</v>
       </c>
-    </row>
-    <row r="267" spans="1:19">
+      <c r="T266" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="U266">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="267" spans="1:21">
       <c r="A267" s="1" t="s">
         <v>241</v>
       </c>
@@ -19126,11 +20681,17 @@
       <c r="R267">
         <v>23.7</v>
       </c>
-      <c r="S267">
+      <c r="S267" s="5">
         <v>629.62</v>
       </c>
-    </row>
-    <row r="268" spans="1:19">
+      <c r="T267" s="4">
+        <v>7.78</v>
+      </c>
+      <c r="U267">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="268" spans="1:21">
       <c r="A268" s="1" t="s">
         <v>242</v>
       </c>
@@ -19185,11 +20746,17 @@
       <c r="R268">
         <v>24.6</v>
       </c>
-      <c r="S268">
+      <c r="S268" s="5">
         <v>141.26</v>
       </c>
-    </row>
-    <row r="269" spans="1:19">
+      <c r="T268" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U268">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21">
       <c r="A269" s="1" t="s">
         <v>243</v>
       </c>
@@ -19244,11 +20811,17 @@
       <c r="R269">
         <v>24.6</v>
       </c>
-      <c r="S269">
+      <c r="S269" s="5">
         <v>141.26</v>
       </c>
-    </row>
-    <row r="270" spans="1:19">
+      <c r="T269" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U269">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="270" spans="1:21">
       <c r="A270" s="1" t="s">
         <v>244</v>
       </c>
@@ -19303,11 +20876,17 @@
       <c r="R270">
         <v>25.2</v>
       </c>
-      <c r="S270">
+      <c r="S270" s="5">
         <v>309.79000000000002</v>
       </c>
-    </row>
-    <row r="271" spans="1:19">
+      <c r="T270" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U270">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21">
       <c r="A271" s="1" t="s">
         <v>245</v>
       </c>
@@ -19362,11 +20941,17 @@
       <c r="R271">
         <v>25.2</v>
       </c>
-      <c r="S271">
+      <c r="S271" s="5">
         <v>309.79000000000002</v>
       </c>
-    </row>
-    <row r="272" spans="1:19">
+      <c r="T271" s="4">
+        <v>7.84</v>
+      </c>
+      <c r="U271">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="272" spans="1:21">
       <c r="A272" s="1" t="s">
         <v>246</v>
       </c>
@@ -19421,11 +21006,17 @@
       <c r="R272">
         <v>25.2</v>
       </c>
-      <c r="S272">
+      <c r="S272" s="5">
         <v>132.76</v>
       </c>
-    </row>
-    <row r="273" spans="1:19">
+      <c r="T272" s="4">
+        <v>7.74</v>
+      </c>
+      <c r="U272">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="273" spans="1:21">
       <c r="A273" s="1" t="s">
         <v>247</v>
       </c>
@@ -19480,11 +21071,17 @@
       <c r="R273">
         <v>25.2</v>
       </c>
-      <c r="S273">
+      <c r="S273" s="5">
         <v>132.76</v>
       </c>
-    </row>
-    <row r="274" spans="1:19">
+      <c r="T273" s="4">
+        <v>7.74</v>
+      </c>
+      <c r="U273">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="274" spans="1:21">
       <c r="A274" s="1" t="s">
         <v>248</v>
       </c>
@@ -19539,11 +21136,17 @@
       <c r="R274">
         <v>21.1</v>
       </c>
-      <c r="S274">
+      <c r="S274" s="5">
         <v>128.37</v>
       </c>
-    </row>
-    <row r="275" spans="1:19">
+      <c r="T274" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U274">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="275" spans="1:21">
       <c r="A275" s="1" t="s">
         <v>249</v>
       </c>
@@ -19598,11 +21201,17 @@
       <c r="R275">
         <v>21.1</v>
       </c>
-      <c r="S275">
+      <c r="S275" s="5">
         <v>128.37</v>
       </c>
-    </row>
-    <row r="276" spans="1:19">
+      <c r="T275" s="4">
+        <v>7.8</v>
+      </c>
+      <c r="U275">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="276" spans="1:21">
       <c r="A276" s="1" t="s">
         <v>250</v>
       </c>
@@ -19657,11 +21266,17 @@
       <c r="R276">
         <v>23.5</v>
       </c>
-      <c r="S276">
+      <c r="S276" s="5">
         <v>222.52</v>
       </c>
-    </row>
-    <row r="277" spans="1:19">
+      <c r="T276" s="4">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="U276">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="277" spans="1:21">
       <c r="A277" s="1" t="s">
         <v>251</v>
       </c>
@@ -19716,11 +21331,17 @@
       <c r="R277">
         <v>23.5</v>
       </c>
-      <c r="S277">
+      <c r="S277" s="5">
         <v>222.52</v>
       </c>
-    </row>
-    <row r="278" spans="1:19">
+      <c r="T277" s="4">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="U277">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="278" spans="1:21">
       <c r="A278" s="1" t="s">
         <v>252</v>
       </c>
@@ -19775,11 +21396,17 @@
       <c r="R278">
         <v>25.1</v>
       </c>
-      <c r="S278">
+      <c r="S278" s="5">
         <v>240.29</v>
       </c>
-    </row>
-    <row r="279" spans="1:19">
+      <c r="T278" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U278">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="279" spans="1:21">
       <c r="A279" s="1" t="s">
         <v>253</v>
       </c>
@@ -19834,11 +21461,17 @@
       <c r="R279">
         <v>25.1</v>
       </c>
-      <c r="S279">
+      <c r="S279" s="5">
         <v>240.29</v>
       </c>
-    </row>
-    <row r="280" spans="1:19">
+      <c r="T279" s="4">
+        <v>7.43</v>
+      </c>
+      <c r="U279">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="280" spans="1:21">
       <c r="A280" s="1" t="s">
         <v>254</v>
       </c>
@@ -19888,16 +21521,22 @@
         <v>490</v>
       </c>
       <c r="Q280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R280">
         <v>22.7</v>
       </c>
-      <c r="S280">
+      <c r="S280" s="5">
         <v>14.08</v>
       </c>
-    </row>
-    <row r="281" spans="1:19">
+      <c r="T280" s="4">
+        <v>8.16</v>
+      </c>
+      <c r="U280">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="281" spans="1:21">
       <c r="A281" s="1" t="s">
         <v>255</v>
       </c>
@@ -19952,11 +21591,17 @@
       <c r="R281">
         <v>22.7</v>
       </c>
-      <c r="S281">
+      <c r="S281" s="5">
         <v>14.08</v>
       </c>
-    </row>
-    <row r="282" spans="1:19">
+      <c r="T281" s="4">
+        <v>8.16</v>
+      </c>
+      <c r="U281">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="282" spans="1:21">
       <c r="A282" s="1" t="s">
         <v>256</v>
       </c>
@@ -20011,11 +21656,17 @@
       <c r="R282">
         <v>23</v>
       </c>
-      <c r="S282">
+      <c r="S282" s="5">
         <v>49.24</v>
       </c>
-    </row>
-    <row r="283" spans="1:19">
+      <c r="T282" s="4">
+        <v>7.76</v>
+      </c>
+      <c r="U282">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="283" spans="1:21">
       <c r="A283" s="1" t="s">
         <v>257</v>
       </c>
@@ -20070,11 +21721,17 @@
       <c r="R283">
         <v>23</v>
       </c>
-      <c r="S283">
+      <c r="S283" s="5">
         <v>49.24</v>
       </c>
-    </row>
-    <row r="284" spans="1:19">
+      <c r="T283" s="4">
+        <v>7.76</v>
+      </c>
+      <c r="U283">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="284" spans="1:21">
       <c r="A284" s="1" t="s">
         <v>258</v>
       </c>
@@ -20129,11 +21786,17 @@
       <c r="R284">
         <v>24</v>
       </c>
-      <c r="S284">
+      <c r="S284" s="5">
         <v>102.93</v>
       </c>
-    </row>
-    <row r="285" spans="1:19">
+      <c r="T284" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="U284">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="285" spans="1:21">
       <c r="A285" s="1" t="s">
         <v>259</v>
       </c>
@@ -20188,11 +21851,17 @@
       <c r="R285">
         <v>24</v>
       </c>
-      <c r="S285">
+      <c r="S285" s="5">
         <v>102.93</v>
       </c>
-    </row>
-    <row r="286" spans="1:19">
+      <c r="T285" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="U285">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="286" spans="1:21">
       <c r="A286" s="1" t="s">
         <v>260</v>
       </c>
@@ -20247,11 +21916,17 @@
       <c r="R286">
         <v>22.8</v>
       </c>
-      <c r="S286">
+      <c r="S286" s="5">
         <v>243.5</v>
       </c>
-    </row>
-    <row r="287" spans="1:19">
+      <c r="T286" s="4">
+        <v>8.41</v>
+      </c>
+      <c r="U286">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="287" spans="1:21">
       <c r="A287" s="1" t="s">
         <v>261</v>
       </c>
@@ -20306,11 +21981,17 @@
       <c r="R287">
         <v>24.2</v>
       </c>
-      <c r="S287">
+      <c r="S287" s="5">
         <v>329.71</v>
       </c>
-    </row>
-    <row r="288" spans="1:19">
+      <c r="T287" s="4">
+        <v>8.08</v>
+      </c>
+      <c r="U287">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="288" spans="1:21">
       <c r="A288" s="1" t="s">
         <v>262</v>
       </c>
@@ -20365,11 +22046,17 @@
       <c r="R288">
         <v>23.5</v>
       </c>
-      <c r="S288">
+      <c r="S288" s="5">
         <v>222.52</v>
       </c>
-    </row>
-    <row r="289" spans="1:19">
+      <c r="T288" s="4">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="U288">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="289" spans="1:21">
       <c r="A289" s="1" t="s">
         <v>263</v>
       </c>
@@ -20424,11 +22111,17 @@
       <c r="R289">
         <v>24</v>
       </c>
-      <c r="S289">
+      <c r="S289" s="5">
         <v>102.93</v>
       </c>
-    </row>
-    <row r="290" spans="1:19">
+      <c r="T289" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="U289">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="290" spans="1:21">
       <c r="A290" s="1" t="s">
         <v>264</v>
       </c>
@@ -20439,7 +22132,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="291" spans="1:19">
+    <row r="291" spans="1:21">
       <c r="A291" s="1" t="s">
         <v>265</v>
       </c>
@@ -20450,7 +22143,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="292" spans="1:19">
+    <row r="292" spans="1:21">
       <c r="A292" s="1" t="s">
         <v>266</v>
       </c>
@@ -20461,7 +22154,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="293" spans="1:19">
+    <row r="293" spans="1:21">
       <c r="A293" s="1" t="s">
         <v>267</v>
       </c>
@@ -20472,7 +22165,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="294" spans="1:19">
+    <row r="294" spans="1:21">
       <c r="A294" s="1" t="s">
         <v>268</v>
       </c>
@@ -20483,7 +22176,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="295" spans="1:19">
+    <row r="295" spans="1:21">
       <c r="A295" s="1" t="s">
         <v>269</v>
       </c>
@@ -20494,7 +22187,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="296" spans="1:19">
+    <row r="296" spans="1:21">
       <c r="A296" s="1" t="s">
         <v>270</v>
       </c>
@@ -20505,7 +22198,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="297" spans="1:19">
+    <row r="297" spans="1:21">
       <c r="A297" s="1" t="s">
         <v>271</v>
       </c>
@@ -20516,7 +22209,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="298" spans="1:19">
+    <row r="298" spans="1:21">
       <c r="A298" s="1" t="s">
         <v>272</v>
       </c>

--- a/08_sampledata.xlsx
+++ b/08_sampledata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/65f33c3464bcf092/Research/2018-2022_Sado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="335" documentId="8_{C96D46A6-B296-FB4D-A5F1-3DE4A23156A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71A64F87-3ED3-514B-8C07-460D991ADC10}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="8_{C96D46A6-B296-FB4D-A5F1-3DE4A23156A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81ED2751-6676-CC46-91BB-99B45ABCFA29}"/>
   <bookViews>
     <workbookView xWindow="7940" yWindow="600" windowWidth="27160" windowHeight="27760" xr2:uid="{3521B622-29B9-CA4D-8B15-F4EE5C51B8FD}"/>
   </bookViews>
@@ -2898,10 +2898,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>disch</t>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>sample</t>
     <phoneticPr fontId="18"/>
   </si>
@@ -2911,6 +2907,10 @@
   </si>
   <si>
     <t>ec</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>disc</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -2919,9 +2919,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="182" formatCode="0.0_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -3519,13 +3519,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3931,7 +3931,7 @@
   <sheetData>
     <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B1" t="s">
         <v>474</v>
@@ -3985,13 +3985,13 @@
         <v>925</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="T1" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="U1" t="s">
         <v>928</v>
-      </c>
-      <c r="U1" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="2" spans="1:21">
